--- a/Coastal_Bad_Levo1.xlsx
+++ b/Coastal_Bad_Levo1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bart076\Documents\GitHub\Coastal_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/edc05105a1ab0e97/Documents/GitHub/CoastalFires/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4186EA4C-6139-4C3E-A92A-6F88167EEABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{4186EA4C-6139-4C3E-A92A-6F88167EEABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4CE36A6-EEDF-4FA5-ACCB-081AE0EE62EB}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DB4A0C19-BBA7-4099-8C32-C32D7963ECEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB4A0C19-BBA7-4099-8C32-C32D7963ECEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="36">
   <si>
     <t>Watershed</t>
   </si>
@@ -137,106 +137,10 @@
     <t>H</t>
   </si>
   <si>
-    <t>804.30 ± 77.36</t>
-  </si>
-  <si>
-    <t>28.665 ± 8.478</t>
-  </si>
-  <si>
-    <t>0.991 ± 0.175</t>
-  </si>
-  <si>
-    <t>0.125 ± 0.034</t>
-  </si>
-  <si>
-    <t>3.71 ± 1.71</t>
-  </si>
-  <si>
-    <t>828.4 ± 160.3</t>
-  </si>
-  <si>
-    <t>885.3 ± 168.6</t>
-  </si>
-  <si>
-    <t>0.936 ± 0.003</t>
-  </si>
-  <si>
-    <t>7.410 ± 0.099</t>
-  </si>
-  <si>
-    <t>0.351 ± 0.026</t>
-  </si>
-  <si>
-    <t>4.750 ± 0.354</t>
-  </si>
-  <si>
-    <t>162.6 ± 12.1</t>
-  </si>
-  <si>
-    <t>391.0 ± 32.2</t>
-  </si>
-  <si>
-    <t>0.416 ± 0.003</t>
-  </si>
-  <si>
-    <t>52.393 ± 1.791</t>
-  </si>
-  <si>
-    <t>3.071 ± 0.146</t>
-  </si>
-  <si>
     <t>ND</t>
   </si>
   <si>
     <t>Pescadero Creek</t>
-  </si>
-  <si>
-    <t>1.30 ± 0.14</t>
-  </si>
-  <si>
-    <t>0.405 ± 0.290</t>
-  </si>
-  <si>
-    <t>0.005 ± 0.001</t>
-  </si>
-  <si>
-    <t>0.400 ± 0.018</t>
-  </si>
-  <si>
-    <t>1.64 ± 0.97</t>
-  </si>
-  <si>
-    <t>2.5 ± 0.5</t>
-  </si>
-  <si>
-    <t>3.2 ± 0.48</t>
-  </si>
-  <si>
-    <t>0.768 ± 0.032</t>
-  </si>
-  <si>
-    <t>2.800 ± 0.042</t>
-  </si>
-  <si>
-    <t>0.165 ± 0.018</t>
-  </si>
-  <si>
-    <t>5.876 ± 0.554</t>
-  </si>
-  <si>
-    <t>67.0 ± 8.2</t>
-  </si>
-  <si>
-    <t>175.3 ± 20.6</t>
-  </si>
-  <si>
-    <t>0.382 ± 0.002</t>
-  </si>
-  <si>
-    <t>19.806 ± 0.000</t>
-  </si>
-  <si>
-    <t>3.072 ± 0.047</t>
   </si>
   <si>
     <t>Majors Creek</t>
@@ -245,109 +149,19 @@
     <t>Laguna Creek</t>
   </si>
   <si>
-    <t>1.28 ± 0.66</t>
-  </si>
-  <si>
-    <t>0.075 ± 0.007</t>
-  </si>
-  <si>
-    <t>0.008 ± 0.004</t>
-  </si>
-  <si>
-    <t>0.605 ± 0.036</t>
-  </si>
-  <si>
-    <t>10.39 ± 5.67</t>
-  </si>
-  <si>
-    <t>4.3 ± 1.8</t>
-  </si>
-  <si>
-    <t>4.3 ± 2.4</t>
-  </si>
-  <si>
-    <t>1.045 ± 0.171</t>
-  </si>
-  <si>
-    <t>0.785 ± 0.148</t>
-  </si>
-  <si>
-    <t>0.024 ± 0.000</t>
-  </si>
-  <si>
-    <t>3.100 ± 0.566</t>
-  </si>
-  <si>
-    <t>9.3 ± 0.4</t>
-  </si>
-  <si>
-    <t>20.4 ± 0.3</t>
-  </si>
-  <si>
-    <t>0.458 ± 0.013</t>
-  </si>
-  <si>
-    <t>7.024 ± 0.163</t>
-  </si>
-  <si>
-    <t>3.947 ± 0.657</t>
-  </si>
-  <si>
     <t>Scott Creek</t>
-  </si>
-  <si>
-    <t>99.20 ± 11.17</t>
-  </si>
-  <si>
-    <t>6.840 ± 4.978</t>
-  </si>
-  <si>
-    <t>0.301 ± 0.122</t>
-  </si>
-  <si>
-    <t>0.298 ± 0.090</t>
-  </si>
-  <si>
-    <t>6.86 ± 6.78</t>
-  </si>
-  <si>
-    <t>225.4 ± 100.1</t>
-  </si>
-  <si>
-    <t>243.2 ±106.6</t>
-  </si>
-  <si>
-    <t>0.925 ± 0.006</t>
-  </si>
-  <si>
-    <t>2.015 ± 0.856</t>
-  </si>
-  <si>
-    <t>0.145 ± 0.023</t>
-  </si>
-  <si>
-    <t>7.651 ± 2.119</t>
-  </si>
-  <si>
-    <t>58.7 ± 10.6</t>
-  </si>
-  <si>
-    <t>152.4 ± 25.5</t>
-  </si>
-  <si>
-    <t>0.385 ± 0.005</t>
-  </si>
-  <si>
-    <t>17.388 ± 4.723</t>
-  </si>
-  <si>
-    <t>3.881 ± 0.630</t>
   </si>
   <si>
     <t>Levoglucosan (ppb)</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>Lagoon</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -359,7 +173,7 @@
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,9 +292,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -518,7 +332,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -624,7 +438,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -766,7 +580,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -774,24 +588,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E92B09EE-B355-4976-86D6-B3CFA19E3FEC}">
-  <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="13.8"/>
+  <dimension ref="A1:Y55"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.20703125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="22.41796875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.1015625" style="8" customWidth="1"/>
-    <col min="4" max="5" width="12.1015625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="8" customWidth="1"/>
+    <col min="4" max="5" width="12.109375" style="6" customWidth="1"/>
     <col min="6" max="6" width="11" style="9" customWidth="1"/>
-    <col min="7" max="7" width="10.41796875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="15.62890625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="16" style="10" customWidth="1"/>
-    <col min="10" max="12" width="16" style="6" customWidth="1"/>
-    <col min="13" max="13" width="16" style="10" customWidth="1"/>
-    <col min="14" max="24" width="16" style="6" customWidth="1"/>
-    <col min="25" max="16384" width="8.89453125" style="6"/>
+    <col min="7" max="8" width="10.44140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="16" style="10" customWidth="1"/>
+    <col min="11" max="13" width="16" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16" style="10" customWidth="1"/>
+    <col min="15" max="25" width="16" style="6" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="24.6">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -814,58 +628,61 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -887,59 +704,62 @@
       <c r="G2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="6">
         <v>1.0051212627340611</v>
       </c>
-      <c r="I2" s="10">
+      <c r="J2" s="10">
         <v>1.44</v>
       </c>
-      <c r="J2" s="9">
+      <c r="K2" s="9">
         <v>0.44</v>
       </c>
-      <c r="K2" s="9">
+      <c r="L2" s="9">
         <v>6.228E-3</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="9">
         <v>0.4325</v>
       </c>
-      <c r="M2" s="10">
+      <c r="N2" s="10">
         <v>1.4154545454545455</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <v>3.1580000000000004</v>
       </c>
-      <c r="O2" s="9">
+      <c r="P2" s="9">
         <v>3.6670000000000003</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="9">
         <v>0.86125799999999997</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <v>1.73</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="S2" s="9">
+      <c r="T2" s="9">
         <v>4</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <v>24.504999999999999</v>
       </c>
-      <c r="U2" s="9">
+      <c r="V2" s="9">
         <v>68.974999999999994</v>
       </c>
-      <c r="V2" s="9">
+      <c r="W2" s="9">
         <v>0.35527734500000002</v>
       </c>
-      <c r="W2" s="9">
+      <c r="X2" s="9">
         <v>12.436199999999999</v>
       </c>
-      <c r="X2" s="9">
+      <c r="Y2" s="9">
         <v>3.1213872832369942</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
@@ -961,59 +781,62 @@
       <c r="G3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="6">
         <v>14.078975009958025</v>
       </c>
-      <c r="I3" s="10">
+      <c r="J3" s="10">
         <v>8</v>
       </c>
-      <c r="J3" s="9">
+      <c r="K3" s="9">
         <v>1.36</v>
       </c>
-      <c r="K3" s="9">
+      <c r="L3" s="9">
         <v>2.6571999999999998E-2</v>
       </c>
-      <c r="L3" s="9">
+      <c r="M3" s="9">
         <v>0.33215</v>
       </c>
-      <c r="M3" s="10">
+      <c r="N3" s="10">
         <v>1.9538235294117645</v>
       </c>
-      <c r="N3" s="9">
+      <c r="O3" s="9">
         <v>16.958000000000002</v>
       </c>
-      <c r="O3" s="9">
+      <c r="P3" s="9">
         <v>16.219000000000001</v>
       </c>
-      <c r="P3" s="9">
+      <c r="Q3" s="9">
         <v>1.045531</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="R3" s="9">
         <v>9.5299999999999994</v>
       </c>
-      <c r="R3" s="9">
+      <c r="S3" s="9">
         <v>0.2742</v>
       </c>
-      <c r="S3" s="9">
+      <c r="T3" s="9">
         <v>2.9</v>
       </c>
-      <c r="T3" s="9">
+      <c r="U3" s="9">
         <v>108.89999999999999</v>
       </c>
-      <c r="U3" s="9">
+      <c r="V3" s="9">
         <v>305.39999999999998</v>
       </c>
-      <c r="V3" s="9">
+      <c r="W3" s="9">
         <v>0.35673594199999997</v>
       </c>
-      <c r="W3" s="9">
+      <c r="X3" s="9">
         <v>47.672099999999993</v>
       </c>
-      <c r="X3" s="9">
+      <c r="Y3" s="9">
         <v>2.1720881427072403</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>23</v>
       </c>
@@ -1035,59 +858,62 @@
       <c r="G4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="6">
         <v>10.834253438310432</v>
       </c>
-      <c r="I4" s="10">
+      <c r="J4" s="10">
         <v>17</v>
       </c>
-      <c r="J4" s="9">
+      <c r="K4" s="9">
         <v>2.29</v>
       </c>
-      <c r="K4" s="9">
+      <c r="L4" s="9">
         <v>3.6337000000000001E-2</v>
       </c>
-      <c r="L4" s="9">
+      <c r="M4" s="9">
         <v>0.2137470588235294</v>
       </c>
-      <c r="M4" s="10">
+      <c r="N4" s="10">
         <v>1.5867685589519651</v>
       </c>
-      <c r="N4" s="9">
+      <c r="O4" s="9">
         <v>23.712</v>
       </c>
-      <c r="O4" s="9">
+      <c r="P4" s="9">
         <v>22.952000000000002</v>
       </c>
-      <c r="P4" s="9">
+      <c r="Q4" s="9">
         <v>1.033096</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="R4" s="9">
         <v>6.73</v>
       </c>
-      <c r="R4" s="9">
+      <c r="S4" s="9">
         <v>0.1439</v>
       </c>
-      <c r="S4" s="9">
+      <c r="T4" s="9">
         <v>2.1</v>
       </c>
-      <c r="T4" s="9">
+      <c r="U4" s="9">
         <v>53.6</v>
       </c>
-      <c r="U4" s="9">
+      <c r="V4" s="9">
         <v>161.1</v>
       </c>
-      <c r="V4" s="9">
+      <c r="W4" s="9">
         <v>0.332838996</v>
       </c>
-      <c r="W4" s="9">
+      <c r="X4" s="9">
         <v>34.544999999999995</v>
       </c>
-      <c r="X4" s="9">
+      <c r="Y4" s="9">
         <v>2.2288261515601779</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>23</v>
       </c>
@@ -1109,59 +935,62 @@
       <c r="G5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="6">
         <v>1.3295934198988206</v>
       </c>
-      <c r="I5" s="10">
+      <c r="J5" s="10">
         <v>1.1100000000000001</v>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="9">
         <v>0.23</v>
       </c>
-      <c r="K5" s="9">
+      <c r="L5" s="9">
         <v>6.4079999999999996E-3</v>
       </c>
-      <c r="L5" s="9">
+      <c r="M5" s="9">
         <v>0.57729729729729728</v>
       </c>
-      <c r="M5" s="10">
+      <c r="N5" s="10">
         <v>2.7860869565217392</v>
       </c>
-      <c r="N5" s="9">
+      <c r="O5" s="9">
         <v>3.3240000000000003</v>
       </c>
-      <c r="O5" s="9">
+      <c r="P5" s="9">
         <v>3.7160000000000002</v>
       </c>
-      <c r="P5" s="9">
+      <c r="Q5" s="9">
         <v>0.89453499999999997</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="R5" s="9">
         <v>1.95</v>
       </c>
-      <c r="R5" s="9">
+      <c r="S5" s="9">
         <v>8.2699999999999996E-2</v>
       </c>
-      <c r="S5" s="9">
+      <c r="T5" s="9">
         <v>4.2</v>
       </c>
-      <c r="T5" s="9">
+      <c r="U5" s="9">
         <v>30.5</v>
       </c>
-      <c r="U5" s="9">
+      <c r="V5" s="9">
         <v>83.8</v>
       </c>
-      <c r="V5" s="9">
+      <c r="W5" s="9">
         <v>0.36424948099999999</v>
       </c>
-      <c r="W5" s="9">
+      <c r="X5" s="9">
         <v>12.436199999999999</v>
       </c>
-      <c r="X5" s="9">
+      <c r="Y5" s="9">
         <v>2.7692307692307692</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -1183,59 +1012,62 @@
       <c r="G6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="6">
         <v>6.3074711481093981</v>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="10">
         <v>27.31</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="9">
         <v>2.17</v>
       </c>
-      <c r="K6" s="9">
+      <c r="L6" s="9">
         <v>2.8566000000000001E-2</v>
       </c>
-      <c r="L6" s="9">
+      <c r="M6" s="9">
         <v>0.10459904796777737</v>
       </c>
-      <c r="M6" s="10">
+      <c r="N6" s="10">
         <v>1.3164055299539172</v>
       </c>
-      <c r="N6" s="9">
+      <c r="O6" s="9">
         <v>18.576999999999998</v>
       </c>
-      <c r="O6" s="9">
+      <c r="P6" s="9">
         <v>17.321999999999999</v>
       </c>
-      <c r="P6" s="9">
+      <c r="Q6" s="9">
         <v>1.0724629999999999</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="R6" s="9">
         <v>4.6900000000000004</v>
       </c>
-      <c r="R6" s="9">
+      <c r="S6" s="9">
         <v>0.16</v>
       </c>
-      <c r="S6" s="9">
+      <c r="T6" s="9">
         <v>3.4</v>
       </c>
-      <c r="T6" s="9">
+      <c r="U6" s="9">
         <v>59.1</v>
       </c>
-      <c r="U6" s="9">
+      <c r="V6" s="9">
         <v>167.9</v>
       </c>
-      <c r="V6" s="9">
+      <c r="W6" s="9">
         <v>0.35178255800000002</v>
       </c>
-      <c r="W6" s="9">
+      <c r="X6" s="9">
         <v>30.629899999999999</v>
       </c>
-      <c r="X6" s="9">
+      <c r="Y6" s="9">
         <v>2.8358208955223878</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
@@ -1257,59 +1089,62 @@
       <c r="G7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6">
         <v>3.5692426998409408</v>
       </c>
-      <c r="I7" s="10">
+      <c r="J7" s="10">
         <v>34.44</v>
       </c>
-      <c r="J7" s="9">
+      <c r="K7" s="9">
         <v>5.73</v>
       </c>
-      <c r="K7" s="9">
+      <c r="L7" s="9">
         <v>6.5972000000000003E-2</v>
       </c>
-      <c r="L7" s="9">
+      <c r="M7" s="9">
         <v>0.1915563298490128</v>
       </c>
-      <c r="M7" s="10">
+      <c r="N7" s="10">
         <v>1.1513438045375217</v>
       </c>
-      <c r="N7" s="9">
+      <c r="O7" s="9">
         <v>46.718999999999994</v>
       </c>
-      <c r="O7" s="9">
+      <c r="P7" s="9">
         <v>42.668999999999997</v>
       </c>
-      <c r="P7" s="9">
+      <c r="Q7" s="9">
         <v>1.0949329999999999</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="R7" s="9">
         <v>3.67</v>
       </c>
-      <c r="R7" s="9">
+      <c r="S7" s="9">
         <v>0.13850000000000001</v>
       </c>
-      <c r="S7" s="9">
+      <c r="T7" s="9">
         <v>3.8</v>
       </c>
-      <c r="T7" s="9">
+      <c r="U7" s="9">
         <v>54.4</v>
       </c>
-      <c r="U7" s="9">
+      <c r="V7" s="9">
         <v>151.5</v>
       </c>
-      <c r="V7" s="9">
+      <c r="W7" s="9">
         <v>0.35915212899999999</v>
       </c>
-      <c r="W7" s="9">
+      <c r="X7" s="9">
         <v>28.096599999999999</v>
       </c>
-      <c r="X7" s="9">
+      <c r="Y7" s="9">
         <v>3.3242506811989099</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
@@ -1331,59 +1166,62 @@
       <c r="G8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="6">
         <v>5.2311732609287329</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="J8" s="10">
+        <v>804.3</v>
+      </c>
+      <c r="K8" s="9">
+        <v>28.664999999999999</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="N8" s="10">
+        <v>3.71</v>
+      </c>
+      <c r="O8" s="9">
+        <v>828.4</v>
+      </c>
+      <c r="P8" s="9">
+        <v>885.3</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="R8" s="9">
+        <v>7.41</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="T8" s="9">
+        <v>4.75</v>
+      </c>
+      <c r="U8" s="9">
+        <v>162.6</v>
+      </c>
+      <c r="V8" s="9">
+        <v>391</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="X8" s="9">
+        <v>52.393000000000001</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>3.0710000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
@@ -1405,56 +1243,62 @@
       <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="10">
+      <c r="H9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="6">
+        <v>-9999</v>
+      </c>
+      <c r="J9" s="10">
         <v>741.33</v>
       </c>
-      <c r="J9" s="9">
+      <c r="K9" s="9">
         <v>17.579999999999998</v>
       </c>
-      <c r="K9" s="9">
+      <c r="L9" s="9">
         <v>0.69479900000000006</v>
       </c>
-      <c r="L9" s="9">
+      <c r="M9" s="9">
         <v>9.3723308108399767E-2</v>
       </c>
-      <c r="M9" s="10">
+      <c r="N9" s="10">
         <v>3.9522127417519917</v>
       </c>
-      <c r="N9" s="9">
+      <c r="O9" s="9">
         <v>544.81200000000001</v>
       </c>
-      <c r="O9" s="9">
+      <c r="P9" s="9">
         <v>618.56999999999994</v>
       </c>
-      <c r="P9" s="9">
+      <c r="Q9" s="9">
         <v>0.88075999999999999</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="R9" s="9">
         <v>7.97</v>
       </c>
-      <c r="R9" s="9">
+      <c r="S9" s="9">
         <v>0.41799999999999998</v>
       </c>
-      <c r="S9" s="9">
+      <c r="T9" s="9">
         <v>5.2</v>
       </c>
-      <c r="T9" s="9">
+      <c r="U9" s="9">
         <v>213.352</v>
       </c>
-      <c r="U9" s="9">
+      <c r="V9" s="9">
         <v>455.24399999999997</v>
       </c>
-      <c r="V9" s="9">
+      <c r="W9" s="9">
         <v>0.468654709</v>
       </c>
-      <c r="W9" s="9">
+      <c r="X9" s="9">
         <v>62.180999999999997</v>
       </c>
-      <c r="X9" s="9">
+      <c r="Y9" s="9">
         <v>3.3877038895859477</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
@@ -1476,59 +1320,62 @@
       <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="6">
         <v>1.669893487169178</v>
       </c>
-      <c r="I10" s="10">
+      <c r="J10" s="10">
         <v>25.87</v>
       </c>
-      <c r="J10" s="9">
+      <c r="K10" s="9">
         <v>3.1</v>
       </c>
-      <c r="K10" s="9">
+      <c r="L10" s="9">
         <v>3.4042000000000003E-2</v>
       </c>
-      <c r="L10" s="9">
+      <c r="M10" s="9">
         <v>0.13158871279474296</v>
       </c>
-      <c r="M10" s="10">
+      <c r="N10" s="10">
         <v>1.0981290322580646</v>
       </c>
-      <c r="N10" s="9">
+      <c r="O10" s="9">
         <v>21.864000000000001</v>
       </c>
-      <c r="O10" s="9">
+      <c r="P10" s="9">
         <v>21.597000000000001</v>
       </c>
-      <c r="P10" s="9">
+      <c r="Q10" s="9">
         <v>1.012359</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="R10" s="9">
         <v>4.2699999999999996</v>
       </c>
-      <c r="R10" s="9">
+      <c r="S10" s="9">
         <v>0.22259999999999999</v>
       </c>
-      <c r="S10" s="9">
+      <c r="T10" s="9">
         <v>5.2</v>
       </c>
-      <c r="T10" s="9">
+      <c r="U10" s="9">
         <v>101.55500000000001</v>
       </c>
-      <c r="U10" s="9">
+      <c r="V10" s="9">
         <v>234.94300000000001</v>
       </c>
-      <c r="V10" s="9">
+      <c r="W10" s="9">
         <v>0.43225571099999999</v>
       </c>
-      <c r="W10" s="9">
+      <c r="X10" s="9">
         <v>32.472299999999997</v>
       </c>
-      <c r="X10" s="9">
+      <c r="Y10" s="9">
         <v>3.3021077283372362</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
@@ -1550,59 +1397,62 @@
       <c r="G11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="6">
         <v>2.2871819812875005</v>
       </c>
-      <c r="I11" s="10">
+      <c r="J11" s="10">
         <v>12.47</v>
       </c>
-      <c r="J11" s="9">
+      <c r="K11" s="9">
         <v>4.55</v>
       </c>
-      <c r="K11" s="9">
+      <c r="L11" s="9">
         <v>4.2439999999999999E-2</v>
       </c>
-      <c r="L11" s="9">
+      <c r="M11" s="9">
         <v>0.34033680834001601</v>
       </c>
-      <c r="M11" s="10">
+      <c r="N11" s="10">
         <v>0.93274725274725268</v>
       </c>
-      <c r="N11" s="9">
+      <c r="O11" s="9">
         <v>29.206</v>
       </c>
-      <c r="O11" s="9">
+      <c r="P11" s="9">
         <v>26.061</v>
       </c>
-      <c r="P11" s="9">
+      <c r="Q11" s="9">
         <v>1.12066</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="R11" s="9">
         <v>3.24</v>
       </c>
-      <c r="R11" s="9">
+      <c r="S11" s="9">
         <v>0.18509999999999999</v>
       </c>
-      <c r="S11" s="9">
+      <c r="T11" s="9">
         <v>5.7</v>
       </c>
-      <c r="T11" s="9">
+      <c r="U11" s="9">
         <v>78.100000000000009</v>
       </c>
-      <c r="U11" s="9">
+      <c r="V11" s="9">
         <v>197</v>
       </c>
-      <c r="V11" s="9">
+      <c r="W11" s="9">
         <v>0.39646014499999999</v>
       </c>
-      <c r="W11" s="9">
+      <c r="X11" s="9">
         <v>24.411799999999996</v>
       </c>
-      <c r="X11" s="9">
+      <c r="Y11" s="9">
         <v>3.2716049382716044</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -1624,61 +1474,64 @@
       <c r="G12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="6">
         <v>1.0367770829452572</v>
       </c>
-      <c r="I12" s="10">
+      <c r="J12" s="10">
         <v>4.43</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="9">
         <v>0.3</v>
       </c>
-      <c r="K12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>43</v>
+      <c r="L12" s="9">
+        <v>-9999</v>
+      </c>
+      <c r="M12" s="9">
+        <v>-9999</v>
+      </c>
+      <c r="N12" s="9">
+        <v>-9999</v>
+      </c>
+      <c r="O12" s="9">
+        <v>-9999</v>
+      </c>
+      <c r="P12" s="9">
+        <v>-9999</v>
       </c>
       <c r="Q12" s="9">
+        <v>-9999</v>
+      </c>
+      <c r="R12" s="9">
         <v>1.91</v>
       </c>
-      <c r="R12" s="9">
+      <c r="S12" s="9">
         <v>0.1007</v>
       </c>
-      <c r="S12" s="9">
+      <c r="T12" s="9">
         <v>5.3</v>
       </c>
-      <c r="T12" s="9">
+      <c r="U12" s="9">
         <v>41.5</v>
       </c>
-      <c r="U12" s="9">
+      <c r="V12" s="9">
         <v>100.3</v>
       </c>
-      <c r="V12" s="9">
+      <c r="W12" s="9">
         <v>0.413498386</v>
       </c>
-      <c r="W12" s="9">
+      <c r="X12" s="9">
         <v>14.048299999999999</v>
       </c>
-      <c r="X12" s="9">
+      <c r="Y12" s="9">
         <v>3.1937172774869111</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B13" s="7">
         <v>44111</v>
@@ -1698,61 +1551,64 @@
       <c r="G13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="6">
         <v>1.7252911725387712</v>
       </c>
-      <c r="I13" s="10">
+      <c r="J13" s="10">
         <v>1.45</v>
       </c>
-      <c r="J13" s="9">
+      <c r="K13" s="9">
         <v>0.43</v>
       </c>
-      <c r="K13" s="9">
+      <c r="L13" s="9">
         <v>5.6519999999999999E-3</v>
       </c>
-      <c r="L13" s="9">
+      <c r="M13" s="9">
         <v>0.38979310344827584</v>
       </c>
-      <c r="M13" s="10">
+      <c r="N13" s="10">
         <v>1.3144186046511628</v>
       </c>
-      <c r="N13" s="9">
+      <c r="O13" s="9">
         <v>2.581</v>
       </c>
-      <c r="O13" s="9">
+      <c r="P13" s="9">
         <v>3.5599999999999996</v>
       </c>
-      <c r="P13" s="9">
+      <c r="Q13" s="9">
         <v>0.72508099999999998</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="R13" s="9">
         <v>3.48</v>
       </c>
-      <c r="R13" s="9">
+      <c r="S13" s="9">
         <v>0.1522</v>
       </c>
-      <c r="S13" s="9">
+      <c r="T13" s="9">
         <v>4.4000000000000004</v>
       </c>
-      <c r="T13" s="9">
+      <c r="U13" s="9">
         <v>54.699999999999996</v>
       </c>
-      <c r="U13" s="9">
+      <c r="V13" s="9">
         <v>170.4</v>
       </c>
-      <c r="V13" s="9">
+      <c r="W13" s="9">
         <v>0.32129238799999998</v>
       </c>
-      <c r="W13" s="9">
+      <c r="X13" s="9">
         <v>22.799700000000001</v>
       </c>
-      <c r="X13" s="9">
+      <c r="Y13" s="9">
         <v>2.8448275862068968</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7">
         <v>44152</v>
@@ -1772,61 +1628,64 @@
       <c r="G14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="6">
         <v>4.5980568567048117</v>
       </c>
-      <c r="I14" s="10">
+      <c r="J14" s="10">
         <v>3.52</v>
       </c>
-      <c r="J14" s="9">
+      <c r="K14" s="9">
         <v>0.87</v>
       </c>
-      <c r="K14" s="9">
+      <c r="L14" s="9">
         <v>8.3160000000000005E-3</v>
       </c>
-      <c r="L14" s="9">
+      <c r="M14" s="9">
         <v>0.23625000000000002</v>
       </c>
-      <c r="M14" s="10">
+      <c r="N14" s="10">
         <v>0.9558620689655174</v>
       </c>
-      <c r="N14" s="9">
+      <c r="O14" s="9">
         <v>4.22</v>
       </c>
-      <c r="O14" s="9">
+      <c r="P14" s="9">
         <v>5.1339999999999995</v>
       </c>
-      <c r="P14" s="9">
+      <c r="Q14" s="9">
         <v>0.82189900000000005</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="R14" s="9">
         <v>4.95</v>
       </c>
-      <c r="R14" s="9">
+      <c r="S14" s="9">
         <v>0.1817</v>
       </c>
-      <c r="S14" s="9">
+      <c r="T14" s="9">
         <v>3.7</v>
       </c>
-      <c r="T14" s="9">
+      <c r="U14" s="9">
         <v>66.199999999999989</v>
       </c>
-      <c r="U14" s="9">
+      <c r="V14" s="9">
         <v>200.3</v>
       </c>
-      <c r="V14" s="9">
+      <c r="W14" s="9">
         <v>0.33048951900000001</v>
       </c>
-      <c r="W14" s="9">
+      <c r="X14" s="9">
         <v>30.860199999999999</v>
       </c>
-      <c r="X14" s="9">
+      <c r="Y14" s="9">
         <v>2.7070707070707072</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B15" s="7">
         <v>44153</v>
@@ -1846,61 +1705,64 @@
       <c r="G15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="6">
         <v>2.0893331049675252</v>
       </c>
-      <c r="I15" s="10">
+      <c r="J15" s="10">
         <v>1.45</v>
       </c>
-      <c r="J15" s="9">
+      <c r="K15" s="9">
         <v>0.36</v>
       </c>
-      <c r="K15" s="9">
+      <c r="L15" s="9">
         <v>4.7219999999999996E-3</v>
       </c>
-      <c r="L15" s="9">
+      <c r="M15" s="9">
         <v>0.3256551724137931</v>
       </c>
-      <c r="M15" s="10">
+      <c r="N15" s="10">
         <v>1.3116666666666665</v>
       </c>
-      <c r="N15" s="9">
+      <c r="O15" s="9">
         <v>2.1679999999999997</v>
       </c>
-      <c r="O15" s="9">
+      <c r="P15" s="9">
         <v>2.879</v>
       </c>
-      <c r="P15" s="9">
+      <c r="Q15" s="9">
         <v>0.75309499999999996</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="R15" s="9">
         <v>4.46</v>
       </c>
-      <c r="R15" s="9">
+      <c r="S15" s="9">
         <v>0.20549999999999999</v>
       </c>
-      <c r="S15" s="9">
+      <c r="T15" s="9">
         <v>4.5999999999999996</v>
       </c>
-      <c r="T15" s="9">
+      <c r="U15" s="9">
         <v>78.100000000000009</v>
       </c>
-      <c r="U15" s="9">
+      <c r="V15" s="9">
         <v>228.4</v>
       </c>
-      <c r="V15" s="9">
+      <c r="W15" s="9">
         <v>0.34203080899999999</v>
       </c>
-      <c r="W15" s="9">
+      <c r="X15" s="9">
         <v>29.708699999999997</v>
       </c>
-      <c r="X15" s="9">
+      <c r="Y15" s="9">
         <v>2.8923766816143499</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B16" s="7">
         <v>44176</v>
@@ -1920,61 +1782,64 @@
       <c r="G16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="6">
         <v>1.6936353523275751</v>
       </c>
-      <c r="I16" s="10">
+      <c r="J16" s="10">
         <v>0.9</v>
       </c>
-      <c r="J16" s="9">
+      <c r="K16" s="9">
         <v>0.27</v>
       </c>
-      <c r="K16" s="9">
+      <c r="L16" s="9">
         <v>2.761E-3</v>
       </c>
-      <c r="L16" s="9">
+      <c r="M16" s="9">
         <v>0.30677777777777776</v>
       </c>
-      <c r="M16" s="10">
+      <c r="N16" s="10">
         <v>1.0225925925925925</v>
       </c>
-      <c r="N16" s="9">
+      <c r="O16" s="9">
         <v>1.153</v>
       </c>
-      <c r="O16" s="9">
+      <c r="P16" s="9">
         <v>1.659</v>
       </c>
-      <c r="P16" s="9">
+      <c r="Q16" s="9">
         <v>0.69519299999999995</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="R16" s="9">
         <v>3.25</v>
       </c>
-      <c r="R16" s="9">
+      <c r="S16" s="9">
         <v>0.1817</v>
       </c>
-      <c r="S16" s="9">
+      <c r="T16" s="9">
         <v>5.5910289649999996</v>
       </c>
-      <c r="T16" s="9">
+      <c r="U16" s="9">
         <v>72.5</v>
       </c>
-      <c r="U16" s="9">
+      <c r="V16" s="9">
         <v>197.2</v>
       </c>
-      <c r="V16" s="9">
+      <c r="W16" s="9">
         <v>0.36773461499999999</v>
       </c>
-      <c r="W16" s="9">
+      <c r="X16" s="9">
         <v>20.036099999999998</v>
       </c>
-      <c r="X16" s="9">
+      <c r="Y16" s="9">
         <v>2.6769230769230767</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7">
         <v>44178</v>
@@ -1994,61 +1859,64 @@
       <c r="G17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="6">
         <v>1.8202586331723589</v>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="10">
         <v>1.1299999999999999</v>
       </c>
-      <c r="J17" s="9">
+      <c r="K17" s="9">
         <v>0.19</v>
       </c>
-      <c r="K17" s="9">
+      <c r="L17" s="9">
         <v>4.6129999999999999E-3</v>
       </c>
-      <c r="L17" s="9">
+      <c r="M17" s="9">
         <v>0.40823008849557524</v>
       </c>
-      <c r="M17" s="10">
+      <c r="N17" s="10">
         <v>2.4278947368421053</v>
       </c>
-      <c r="N17" s="9">
+      <c r="O17" s="9">
         <v>2.1819999999999999</v>
       </c>
-      <c r="O17" s="9">
+      <c r="P17" s="9">
         <v>2.7390000000000003</v>
       </c>
-      <c r="P17" s="9">
+      <c r="Q17" s="9">
         <v>0.79665300000000006</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="R17" s="9">
         <v>3.91</v>
       </c>
-      <c r="R17" s="9">
+      <c r="S17" s="9">
         <v>0.17560000000000001</v>
       </c>
-      <c r="S17" s="9">
+      <c r="T17" s="9">
         <v>4.5</v>
       </c>
-      <c r="T17" s="9">
+      <c r="U17" s="9">
         <v>69.400000000000006</v>
       </c>
-      <c r="U17" s="9">
+      <c r="V17" s="9">
         <v>193.89999999999998</v>
       </c>
-      <c r="V17" s="9">
+      <c r="W17" s="9">
         <v>0.357781446</v>
       </c>
-      <c r="W17" s="9">
+      <c r="X17" s="9">
         <v>27.1754</v>
       </c>
-      <c r="X17" s="9">
+      <c r="Y17" s="9">
         <v>3.0179028132992327</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B18" s="7">
         <v>44200</v>
@@ -2068,61 +1936,64 @@
       <c r="G18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="6">
         <v>1.5828399815883887</v>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="10">
         <v>2.4</v>
       </c>
-      <c r="J18" s="9">
+      <c r="K18" s="9">
         <v>0.15</v>
       </c>
-      <c r="K18" s="9">
+      <c r="L18" s="9">
         <v>7.4739999999999997E-3</v>
       </c>
-      <c r="L18" s="9">
+      <c r="M18" s="9">
         <v>0.31141666666666667</v>
       </c>
-      <c r="M18" s="10">
+      <c r="N18" s="10">
         <v>4.9826666666666668</v>
       </c>
-      <c r="N18" s="9">
+      <c r="O18" s="9">
         <v>3.8780000000000001</v>
       </c>
-      <c r="O18" s="9">
+      <c r="P18" s="9">
         <v>4.4470000000000001</v>
       </c>
-      <c r="P18" s="9">
+      <c r="Q18" s="9">
         <v>0.872116</v>
       </c>
-      <c r="Q18" s="9">
+      <c r="R18" s="9">
         <v>3.42</v>
       </c>
-      <c r="R18" s="9">
+      <c r="S18" s="9">
         <v>0.1542</v>
       </c>
-      <c r="S18" s="9">
+      <c r="T18" s="9">
         <v>4.5</v>
       </c>
-      <c r="T18" s="9">
+      <c r="U18" s="9">
         <v>59.5</v>
       </c>
-      <c r="U18" s="9">
+      <c r="V18" s="9">
         <v>166.9</v>
       </c>
-      <c r="V18" s="9">
+      <c r="W18" s="9">
         <v>0.35648927200000002</v>
       </c>
-      <c r="W18" s="9">
+      <c r="X18" s="9">
         <v>23.260300000000001</v>
       </c>
-      <c r="X18" s="9">
+      <c r="Y18" s="9">
         <v>2.9532163742690063</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B19" s="7">
         <v>44223</v>
@@ -2142,61 +2013,64 @@
       <c r="G19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="6">
         <v>2.1605587004427167</v>
       </c>
-      <c r="I19" s="10">
+      <c r="J19" s="10">
         <v>10.63</v>
       </c>
-      <c r="J19" s="9">
+      <c r="K19" s="9">
         <v>1.89</v>
       </c>
-      <c r="K19" s="9">
+      <c r="L19" s="9">
         <v>1.7543E-2</v>
       </c>
-      <c r="L19" s="9">
+      <c r="M19" s="9">
         <v>0.16503292568203196</v>
       </c>
-      <c r="M19" s="10">
+      <c r="N19" s="10">
         <v>0.92820105820105825</v>
       </c>
-      <c r="N19" s="9">
+      <c r="O19" s="9">
         <v>9.3640000000000008</v>
       </c>
-      <c r="O19" s="9">
+      <c r="P19" s="9">
         <v>11.736999999999998</v>
       </c>
-      <c r="P19" s="9">
+      <c r="Q19" s="9">
         <v>0.79776400000000003</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="R19" s="9">
         <v>3.95</v>
       </c>
-      <c r="R19" s="9">
+      <c r="S19" s="9">
         <v>0.20810000000000001</v>
       </c>
-      <c r="S19" s="9">
+      <c r="T19" s="9">
         <v>5.3</v>
       </c>
-      <c r="T19" s="9">
+      <c r="U19" s="9">
         <v>90.930999999999997</v>
       </c>
-      <c r="U19" s="9">
+      <c r="V19" s="9">
         <v>221.66499999999999</v>
       </c>
-      <c r="V19" s="9">
+      <c r="W19" s="9">
         <v>0.41021992400000001</v>
       </c>
-      <c r="W19" s="9">
+      <c r="X19" s="9">
         <v>30.1693</v>
       </c>
-      <c r="X19" s="9">
+      <c r="Y19" s="9">
         <v>3.316455696202532</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7">
         <v>44224</v>
@@ -2217,60 +2091,63 @@
         <v>26</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I20" s="10">
+        <v>34</v>
+      </c>
+      <c r="I20" s="6">
+        <v>-9999</v>
+      </c>
+      <c r="J20" s="10">
         <v>45</v>
       </c>
-      <c r="J20" s="9">
+      <c r="K20" s="9">
         <v>0.85</v>
       </c>
-      <c r="K20" s="9">
+      <c r="L20" s="9">
         <v>3.3496999999999999E-2</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="9">
         <v>7.4437777777777783E-2</v>
       </c>
-      <c r="M20" s="10">
+      <c r="N20" s="10">
         <v>3.9408235294117646</v>
       </c>
-      <c r="N20" s="9">
+      <c r="O20" s="9">
         <v>19.957999999999998</v>
       </c>
-      <c r="O20" s="9">
+      <c r="P20" s="9">
         <v>22.745000000000001</v>
       </c>
-      <c r="P20" s="9">
+      <c r="Q20" s="9">
         <v>0.87745300000000004</v>
       </c>
-      <c r="Q20" s="9">
+      <c r="R20" s="9">
         <v>5.09</v>
       </c>
-      <c r="R20" s="9">
+      <c r="S20" s="9">
         <v>0.28510000000000002</v>
       </c>
-      <c r="S20" s="9">
+      <c r="T20" s="9">
         <v>5.6</v>
       </c>
-      <c r="T20" s="9">
+      <c r="U20" s="9">
         <v>135.494</v>
       </c>
-      <c r="U20" s="9">
+      <c r="V20" s="9">
         <v>305.19200000000001</v>
       </c>
-      <c r="V20" s="9">
+      <c r="W20" s="9">
         <v>0.443964462</v>
       </c>
-      <c r="W20" s="9">
+      <c r="X20" s="9">
         <v>36.1571</v>
       </c>
-      <c r="X20" s="9">
+      <c r="Y20" s="9">
         <v>3.0844793713163066</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B21" s="7">
         <v>44229</v>
@@ -2290,61 +2167,64 @@
       <c r="G21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="6">
         <v>1.923140048858746</v>
       </c>
-      <c r="I21" s="10">
+      <c r="J21" s="10">
         <v>5.9</v>
       </c>
-      <c r="J21" s="9">
+      <c r="K21" s="9">
         <v>1.23</v>
       </c>
-      <c r="K21" s="9">
+      <c r="L21" s="9">
         <v>8.9090000000000003E-3</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>0.151</v>
       </c>
-      <c r="M21" s="10">
+      <c r="N21" s="10">
         <v>0.72430894308943095</v>
       </c>
-      <c r="N21" s="9">
+      <c r="O21" s="9">
         <v>4.7489999999999997</v>
       </c>
-      <c r="O21" s="9">
+      <c r="P21" s="9">
         <v>5.3340000000000005</v>
       </c>
-      <c r="P21" s="9">
+      <c r="Q21" s="9">
         <v>0.89043799999999995</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="R21" s="9">
         <v>4.46</v>
       </c>
-      <c r="R21" s="9">
+      <c r="S21" s="9">
         <v>0.28349999999999997</v>
       </c>
-      <c r="S21" s="9">
+      <c r="T21" s="9">
         <v>6.4</v>
       </c>
-      <c r="T21" s="9">
+      <c r="U21" s="9">
         <v>127.34300000000002</v>
       </c>
-      <c r="U21" s="9">
+      <c r="V21" s="9">
         <v>310.55799999999999</v>
       </c>
-      <c r="V21" s="9">
+      <c r="W21" s="9">
         <v>0.41004586300000001</v>
       </c>
-      <c r="W21" s="9">
+      <c r="X21" s="9">
         <v>32.702599999999997</v>
       </c>
-      <c r="X21" s="9">
+      <c r="Y21" s="9">
         <v>3.1838565022421523</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B22" s="7">
         <v>44273</v>
@@ -2364,61 +2244,64 @@
       <c r="G22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="6">
         <v>0.78353052125568867</v>
       </c>
-      <c r="I22" s="10">
+      <c r="J22" s="10">
         <v>0.8</v>
       </c>
-      <c r="J22" s="9">
+      <c r="K22" s="9">
         <v>1.63</v>
       </c>
-      <c r="K22" s="9">
+      <c r="L22" s="9">
         <v>6.1279999999999998E-3</v>
       </c>
-      <c r="L22" s="9">
+      <c r="M22" s="9">
         <v>0.7659999999999999</v>
       </c>
-      <c r="M22" s="10">
+      <c r="N22" s="10">
         <v>0.37595092024539878</v>
       </c>
-      <c r="N22" s="9">
+      <c r="O22" s="9">
         <v>3.1510000000000002</v>
       </c>
-      <c r="O22" s="9">
+      <c r="P22" s="9">
         <v>3.5550000000000002</v>
       </c>
-      <c r="P22" s="9">
+      <c r="Q22" s="9">
         <v>0.88623300000000005</v>
       </c>
-      <c r="Q22" s="9">
+      <c r="R22" s="9">
         <v>2.75</v>
       </c>
-      <c r="R22" s="9">
+      <c r="S22" s="9">
         <v>0.15529999999999999</v>
       </c>
-      <c r="S22" s="9">
+      <c r="T22" s="9">
         <v>5.6488004299999997</v>
       </c>
-      <c r="T22" s="9">
+      <c r="U22" s="9">
         <v>65.5</v>
       </c>
-      <c r="U22" s="9">
+      <c r="V22" s="9">
         <v>161.80000000000001</v>
       </c>
-      <c r="V22" s="9">
+      <c r="W22" s="9">
         <v>0.40481128999999999</v>
       </c>
-      <c r="W22" s="9">
+      <c r="X22" s="9">
         <v>19.805799999999998</v>
       </c>
-      <c r="X22" s="9">
+      <c r="Y22" s="9">
         <v>3.127272727272727</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B23" s="7">
         <v>44318</v>
@@ -2438,61 +2321,64 @@
       <c r="G23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="6">
         <v>1.0209491728396589</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S23" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="T23" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="U23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="V23" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="W23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="X23" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24">
+      <c r="J23" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="L23" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="N23" s="10">
+        <v>1.64</v>
+      </c>
+      <c r="O23" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="P23" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="R23" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="S23" s="9">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="T23" s="9">
+        <v>5.8760000000000003</v>
+      </c>
+      <c r="U23" s="9">
+        <v>67</v>
+      </c>
+      <c r="V23" s="9">
+        <v>175.3</v>
+      </c>
+      <c r="W23" s="9">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="X23" s="9">
+        <v>19.806000000000001</v>
+      </c>
+      <c r="Y23" s="9">
+        <v>3.0720000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B24" s="7">
         <v>44111</v>
@@ -2512,61 +2398,64 @@
       <c r="G24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="6">
         <v>0.27703739787655213</v>
       </c>
-      <c r="I24" s="10">
+      <c r="J24" s="10">
         <v>0.65</v>
       </c>
-      <c r="J24" s="9">
+      <c r="K24" s="9">
         <v>0.19</v>
       </c>
-      <c r="K24" s="9">
+      <c r="L24" s="9">
         <v>5.6210000000000001E-3</v>
       </c>
-      <c r="L24" s="9">
+      <c r="M24" s="9">
         <v>0.86476923076923073</v>
       </c>
-      <c r="M24" s="10">
+      <c r="N24" s="10">
         <v>2.9584210526315791</v>
       </c>
-      <c r="N24" s="9">
+      <c r="O24" s="9">
         <v>2.931</v>
       </c>
-      <c r="O24" s="9">
+      <c r="P24" s="9">
         <v>3.1719999999999997</v>
       </c>
-      <c r="P24" s="9">
+      <c r="Q24" s="9">
         <v>0.92405499999999996</v>
       </c>
-      <c r="Q24" s="9">
+      <c r="R24" s="9">
         <v>0.86</v>
       </c>
-      <c r="R24" s="9">
+      <c r="S24" s="9">
         <v>2.4E-2</v>
       </c>
-      <c r="S24" s="9">
+      <c r="T24" s="9">
         <v>2.8</v>
       </c>
-      <c r="T24" s="9">
+      <c r="U24" s="9">
         <v>8.2000000000000011</v>
       </c>
-      <c r="U24" s="9">
+      <c r="V24" s="9">
         <v>21.5</v>
       </c>
-      <c r="V24" s="9">
+      <c r="W24" s="9">
         <v>0.38138193500000001</v>
       </c>
-      <c r="W24" s="9">
+      <c r="X24" s="9">
         <v>8.0605000000000011</v>
       </c>
-      <c r="X24" s="9">
+      <c r="Y24" s="9">
         <v>4.0697674418604652</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B25" s="7">
         <v>44152</v>
@@ -2586,61 +2475,64 @@
       <c r="G25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="6">
         <v>2.3504936217098926</v>
       </c>
-      <c r="I25" s="10">
+      <c r="J25" s="10">
         <v>1.91</v>
       </c>
-      <c r="J25" s="9">
+      <c r="K25" s="9">
         <v>0.17</v>
       </c>
-      <c r="K25" s="9">
+      <c r="L25" s="9">
         <v>1.0808999999999999E-2</v>
       </c>
-      <c r="L25" s="9">
+      <c r="M25" s="9">
         <v>0.56591623036649208</v>
       </c>
-      <c r="M25" s="10">
+      <c r="N25" s="10">
         <v>6.3582352941176463</v>
       </c>
-      <c r="N25" s="9">
+      <c r="O25" s="9">
         <v>6.1720000000000006</v>
       </c>
-      <c r="O25" s="9">
+      <c r="P25" s="9">
         <v>6.2760000000000007</v>
       </c>
-      <c r="P25" s="9">
+      <c r="Q25" s="9">
         <v>0.98343100000000006</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="R25" s="9">
         <v>2.0699999999999998</v>
       </c>
-      <c r="R25" s="9">
+      <c r="S25" s="9">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="S25" s="9">
+      <c r="T25" s="9">
         <v>2.8</v>
       </c>
-      <c r="T25" s="9">
+      <c r="U25" s="9">
         <v>23.3</v>
       </c>
-      <c r="U25" s="9">
+      <c r="V25" s="9">
         <v>53.900000000000006</v>
       </c>
-      <c r="V25" s="9">
+      <c r="W25" s="9">
         <v>0.433114997</v>
       </c>
-      <c r="W25" s="9">
+      <c r="X25" s="9">
         <v>12.896799999999999</v>
       </c>
-      <c r="X25" s="9">
+      <c r="Y25" s="9">
         <v>2.7053140096618358</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B26" s="7">
         <v>44153</v>
@@ -2660,61 +2552,64 @@
       <c r="G26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="6">
         <v>5.80889197978306</v>
       </c>
-      <c r="I26" s="10">
+      <c r="J26" s="10">
         <v>3.05</v>
       </c>
-      <c r="J26" s="9">
+      <c r="K26" s="9">
         <v>0.2</v>
       </c>
-      <c r="K26" s="9">
+      <c r="L26" s="9">
         <v>1.1317000000000001E-2</v>
       </c>
-      <c r="L26" s="9">
+      <c r="M26" s="9">
         <v>0.37104918032786888</v>
       </c>
-      <c r="M26" s="10">
+      <c r="N26" s="10">
         <v>5.6585000000000001</v>
       </c>
-      <c r="N26" s="9">
+      <c r="O26" s="9">
         <v>6.4379999999999997</v>
       </c>
-      <c r="O26" s="9">
+      <c r="P26" s="9">
         <v>6.6480000000000006</v>
       </c>
-      <c r="P26" s="9">
+      <c r="Q26" s="9">
         <v>0.96843500000000005</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="R26" s="9">
         <v>3.36</v>
       </c>
-      <c r="R26" s="9">
+      <c r="S26" s="9">
         <v>8.3900000000000002E-2</v>
       </c>
-      <c r="S26" s="9">
+      <c r="T26" s="9">
         <v>2.5</v>
       </c>
-      <c r="T26" s="9">
+      <c r="U26" s="9">
         <v>35.6</v>
       </c>
-      <c r="U26" s="9">
+      <c r="V26" s="9">
         <v>80.3</v>
       </c>
-      <c r="V26" s="9">
+      <c r="W26" s="9">
         <v>0.442540392</v>
       </c>
-      <c r="W26" s="9">
+      <c r="X26" s="9">
         <v>23.03</v>
       </c>
-      <c r="X26" s="9">
+      <c r="Y26" s="9">
         <v>2.9761904761904763</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B27" s="7">
         <v>44176</v>
@@ -2734,61 +2629,64 @@
       <c r="G27" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="6">
         <v>0.10293038671497379</v>
       </c>
-      <c r="I27" s="10">
+      <c r="J27" s="10">
         <v>0.22</v>
       </c>
-      <c r="J27" s="9">
+      <c r="K27" s="9">
         <v>0.16</v>
       </c>
-      <c r="K27" s="9">
+      <c r="L27" s="9">
         <v>3.5119999999999999E-3</v>
       </c>
-      <c r="L27" s="9">
+      <c r="M27" s="9">
         <v>1.5963636363636364</v>
       </c>
-      <c r="M27" s="10">
+      <c r="N27" s="10">
         <v>2.1950000000000003</v>
       </c>
-      <c r="N27" s="9">
+      <c r="O27" s="9">
         <v>1.7689999999999999</v>
       </c>
-      <c r="O27" s="9">
+      <c r="P27" s="9">
         <v>1.8860000000000001</v>
       </c>
-      <c r="P27" s="9">
+      <c r="Q27" s="9">
         <v>0.93782500000000002</v>
       </c>
-      <c r="Q27" s="9">
+      <c r="R27" s="9">
         <v>0.82</v>
       </c>
-      <c r="R27" s="9">
+      <c r="S27" s="9">
         <v>3.9300000000000002E-2</v>
       </c>
-      <c r="S27" s="9">
+      <c r="T27" s="9">
         <v>4.8</v>
       </c>
-      <c r="T27" s="9">
+      <c r="U27" s="9">
         <v>15.4</v>
       </c>
-      <c r="U27" s="9">
+      <c r="V27" s="9">
         <v>35.5</v>
       </c>
-      <c r="V27" s="9">
+      <c r="W27" s="9">
         <v>0.43433993799999998</v>
       </c>
-      <c r="W27" s="9">
+      <c r="X27" s="9">
         <v>8.9817</v>
       </c>
-      <c r="X27" s="9">
+      <c r="Y27" s="9">
         <v>4.7560975609756095</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B28" s="7">
         <v>44178</v>
@@ -2808,61 +2706,64 @@
       <c r="G28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="6">
         <v>3.339738003309769</v>
       </c>
-      <c r="I28" s="10">
+      <c r="J28" s="10">
         <v>10.3</v>
       </c>
-      <c r="J28" s="9">
+      <c r="K28" s="9">
         <v>0.85</v>
       </c>
-      <c r="K28" s="9">
+      <c r="L28" s="9">
         <v>2.8423E-2</v>
       </c>
-      <c r="L28" s="9">
+      <c r="M28" s="9">
         <v>0.27595145631067958</v>
       </c>
-      <c r="M28" s="10">
+      <c r="N28" s="10">
         <v>3.3438823529411765</v>
       </c>
-      <c r="N28" s="9">
+      <c r="O28" s="9">
         <v>17.189</v>
       </c>
-      <c r="O28" s="9">
+      <c r="P28" s="9">
         <v>18.515000000000001</v>
       </c>
-      <c r="P28" s="9">
+      <c r="Q28" s="9">
         <v>0.92835900000000005</v>
       </c>
-      <c r="Q28" s="9">
+      <c r="R28" s="9">
         <v>5.34</v>
       </c>
-      <c r="R28" s="9">
+      <c r="S28" s="9">
         <v>0.15909999999999999</v>
       </c>
-      <c r="S28" s="9">
+      <c r="T28" s="9">
         <v>3</v>
       </c>
-      <c r="T28" s="9">
+      <c r="U28" s="9">
         <v>74.2</v>
       </c>
-      <c r="U28" s="9">
+      <c r="V28" s="9">
         <v>153.10000000000002</v>
       </c>
-      <c r="V28" s="9">
+      <c r="W28" s="9">
         <v>0.48502716299999998</v>
       </c>
-      <c r="W28" s="9">
+      <c r="X28" s="9">
         <v>29.708699999999997</v>
       </c>
-      <c r="X28" s="9">
+      <c r="Y28" s="9">
         <v>2.4157303370786516</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B29" s="7">
         <v>44200</v>
@@ -2882,61 +2783,64 @@
       <c r="G29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="6">
         <v>1.123830588526046</v>
       </c>
-      <c r="I29" s="10">
+      <c r="J29" s="10">
         <v>2.62</v>
       </c>
-      <c r="J29" s="9">
+      <c r="K29" s="9">
         <v>0.53</v>
       </c>
-      <c r="K29" s="9">
+      <c r="L29" s="9">
         <v>1.1789000000000001E-2</v>
       </c>
-      <c r="L29" s="9">
+      <c r="M29" s="9">
         <v>0.44996183206106866</v>
       </c>
-      <c r="M29" s="10">
+      <c r="N29" s="10">
         <v>2.2243396226415095</v>
       </c>
-      <c r="N29" s="9">
+      <c r="O29" s="9">
         <v>6.5739999999999998</v>
       </c>
-      <c r="O29" s="9">
+      <c r="P29" s="9">
         <v>7.1079999999999997</v>
       </c>
-      <c r="P29" s="9">
+      <c r="Q29" s="9">
         <v>0.92494500000000002</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="R29" s="9">
         <v>2.71</v>
       </c>
-      <c r="R29" s="9">
+      <c r="S29" s="9">
         <v>0.10580000000000001</v>
       </c>
-      <c r="S29" s="9">
+      <c r="T29" s="9">
         <v>3.9</v>
       </c>
-      <c r="T29" s="9">
+      <c r="U29" s="9">
         <v>49</v>
       </c>
-      <c r="U29" s="9">
+      <c r="V29" s="9">
         <v>101.4</v>
       </c>
-      <c r="V29" s="9">
+      <c r="W29" s="9">
         <v>0.48383503500000002</v>
       </c>
-      <c r="W29" s="9">
+      <c r="X29" s="9">
         <v>23.03</v>
       </c>
-      <c r="X29" s="9">
+      <c r="Y29" s="9">
         <v>3.6900369003690034</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B30" s="7">
         <v>44223</v>
@@ -2956,61 +2860,64 @@
       <c r="G30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" s="6">
         <v>3.41096359878496</v>
       </c>
-      <c r="I30" s="10">
+      <c r="J30" s="10">
         <v>361</v>
       </c>
-      <c r="J30" s="9">
+      <c r="K30" s="9">
         <v>7.66</v>
       </c>
-      <c r="K30" s="9">
+      <c r="L30" s="9">
         <v>0.19316</v>
       </c>
-      <c r="L30" s="9">
+      <c r="M30" s="9">
         <v>5.3506925207756226E-2</v>
       </c>
-      <c r="M30" s="10">
+      <c r="N30" s="10">
         <v>2.5216710182767623</v>
       </c>
-      <c r="N30" s="9">
+      <c r="O30" s="9">
         <v>146.55799999999999</v>
       </c>
-      <c r="O30" s="9">
+      <c r="P30" s="9">
         <v>141.70699999999999</v>
       </c>
-      <c r="P30" s="9">
+      <c r="Q30" s="9">
         <v>1.034233</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="R30" s="9">
         <v>8.76</v>
       </c>
-      <c r="R30" s="9">
+      <c r="S30" s="9">
         <v>0.34029999999999999</v>
       </c>
-      <c r="S30" s="9">
+      <c r="T30" s="9">
         <v>3.9</v>
       </c>
-      <c r="T30" s="9">
+      <c r="U30" s="9">
         <v>155.29999999999998</v>
       </c>
-      <c r="U30" s="9">
+      <c r="V30" s="9">
         <v>356.9</v>
       </c>
-      <c r="V30" s="9">
+      <c r="W30" s="9">
         <v>0.43514896400000003</v>
       </c>
-      <c r="W30" s="9">
+      <c r="X30" s="9">
         <v>65.174899999999994</v>
       </c>
-      <c r="X30" s="9">
+      <c r="Y30" s="9">
         <v>3.2305936073059356</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B31" s="7">
         <v>44224</v>
@@ -3030,61 +2937,64 @@
       <c r="G31" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="6">
         <v>4.8354755082887824</v>
       </c>
-      <c r="I31" s="10">
+      <c r="J31" s="10">
         <v>883</v>
       </c>
-      <c r="J31" s="9">
+      <c r="K31" s="9">
         <v>8.5500000000000007</v>
       </c>
-      <c r="K31" s="9">
+      <c r="L31" s="9">
         <v>0.56570699999999996</v>
       </c>
-      <c r="L31" s="9">
+      <c r="M31" s="9">
         <v>6.4066477916194783E-2</v>
       </c>
-      <c r="M31" s="10">
+      <c r="N31" s="10">
         <v>6.6164561403508761</v>
       </c>
-      <c r="N31" s="9">
+      <c r="O31" s="9">
         <v>465.97199999999998</v>
       </c>
-      <c r="O31" s="9">
+      <c r="P31" s="9">
         <v>463.911</v>
       </c>
-      <c r="P31" s="9">
+      <c r="Q31" s="9">
         <v>1.0044409999999999</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="R31" s="9">
         <v>10.48</v>
       </c>
-      <c r="R31" s="9">
+      <c r="S31" s="9">
         <v>0.52510000000000001</v>
       </c>
-      <c r="S31" s="9">
+      <c r="T31" s="9">
         <v>5</v>
       </c>
-      <c r="T31" s="9">
+      <c r="U31" s="9">
         <v>274.53300000000002</v>
       </c>
-      <c r="U31" s="9">
+      <c r="V31" s="9">
         <v>582.87699999999995</v>
       </c>
-      <c r="V31" s="9">
+      <c r="W31" s="9">
         <v>0.47099668099999997</v>
       </c>
-      <c r="W31" s="9">
+      <c r="X31" s="9">
         <v>78.762600000000006</v>
       </c>
-      <c r="X31" s="9">
+      <c r="Y31" s="9">
         <v>3.2633587786259541</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B32" s="7">
         <v>44229</v>
@@ -3104,61 +3014,64 @@
       <c r="G32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="6">
         <v>2.540428542977069</v>
       </c>
-      <c r="I32" s="10">
+      <c r="J32" s="10">
         <v>271</v>
       </c>
-      <c r="J32" s="9">
+      <c r="K32" s="9">
         <v>19.34</v>
       </c>
-      <c r="K32" s="9">
+      <c r="L32" s="9">
         <v>0.15363399999999999</v>
       </c>
-      <c r="L32" s="9">
+      <c r="M32" s="9">
         <v>5.6691512915129152E-2</v>
       </c>
-      <c r="M32" s="10">
+      <c r="N32" s="10">
         <v>0.79438469493278174</v>
       </c>
-      <c r="N32" s="9">
+      <c r="O32" s="9">
         <v>112.39200000000001</v>
       </c>
-      <c r="O32" s="9">
+      <c r="P32" s="9">
         <v>112.214</v>
       </c>
-      <c r="P32" s="9">
+      <c r="Q32" s="9">
         <v>1.001582</v>
       </c>
-      <c r="Q32" s="9">
+      <c r="R32" s="9">
         <v>6.97</v>
       </c>
-      <c r="R32" s="9">
+      <c r="S32" s="9">
         <v>0.30869999999999997</v>
       </c>
-      <c r="S32" s="9">
+      <c r="T32" s="9">
         <v>4.4000000000000004</v>
       </c>
-      <c r="T32" s="9">
+      <c r="U32" s="9">
         <v>160.72</v>
       </c>
-      <c r="U32" s="9">
+      <c r="V32" s="9">
         <v>319.786</v>
       </c>
-      <c r="V32" s="9">
+      <c r="W32" s="9">
         <v>0.502587479</v>
       </c>
-      <c r="W32" s="9">
+      <c r="X32" s="9">
         <v>49.284199999999998</v>
       </c>
-      <c r="X32" s="9">
+      <c r="Y32" s="9">
         <v>3.0703012912482066</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B33" s="7">
         <v>44273</v>
@@ -3178,61 +3091,64 @@
       <c r="G33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="6">
         <v>0.98929335262846285</v>
       </c>
-      <c r="I33" s="10">
+      <c r="J33" s="10">
         <v>8.5</v>
       </c>
-      <c r="J33" s="9">
+      <c r="K33" s="9">
         <v>0.8</v>
       </c>
-      <c r="K33" s="9">
+      <c r="L33" s="9">
         <v>2.6457999999999999E-2</v>
       </c>
-      <c r="L33" s="9">
+      <c r="M33" s="9">
         <v>0.31127058823529408</v>
       </c>
-      <c r="M33" s="10">
+      <c r="N33" s="10">
         <v>3.3072499999999998</v>
       </c>
-      <c r="N33" s="9">
+      <c r="O33" s="9">
         <v>16.393999999999998</v>
       </c>
-      <c r="O33" s="9">
+      <c r="P33" s="9">
         <v>16.628</v>
       </c>
-      <c r="P33" s="9">
+      <c r="Q33" s="9">
         <v>0.98593699999999995</v>
       </c>
-      <c r="Q33" s="9">
+      <c r="R33" s="9">
         <v>2.8</v>
       </c>
-      <c r="R33" s="9">
+      <c r="S33" s="9">
         <v>0.1424</v>
       </c>
-      <c r="S33" s="9">
+      <c r="T33" s="9">
         <v>5.0999999999999996</v>
       </c>
-      <c r="T33" s="9">
+      <c r="U33" s="9">
         <v>69.099999999999994</v>
       </c>
-      <c r="U33" s="9">
+      <c r="V33" s="9">
         <v>137.69999999999999</v>
       </c>
-      <c r="V33" s="9">
+      <c r="W33" s="9">
         <v>0.50163649200000004</v>
       </c>
-      <c r="W33" s="9">
+      <c r="X33" s="9">
         <v>20.957299999999996</v>
       </c>
-      <c r="X33" s="9">
+      <c r="Y33" s="9">
         <v>3.25</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B34" s="7">
         <v>44318</v>
@@ -3252,61 +3168,64 @@
       <c r="G34" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="6">
         <v>0.23746762261255694</v>
       </c>
-      <c r="I34" s="10">
+      <c r="J34" s="10">
         <v>3.27</v>
       </c>
-      <c r="J34" s="9">
+      <c r="K34" s="9">
         <v>0.46</v>
       </c>
-      <c r="K34" s="9">
+      <c r="L34" s="9">
         <v>1.1847E-2</v>
       </c>
-      <c r="L34" s="9">
+      <c r="M34" s="9">
         <v>0.36229357798165135</v>
       </c>
-      <c r="M34" s="10">
+      <c r="N34" s="10">
         <v>2.5754347826086956</v>
       </c>
-      <c r="N34" s="9">
+      <c r="O34" s="9">
         <v>6.5919999999999996</v>
       </c>
-      <c r="O34" s="9">
+      <c r="P34" s="9">
         <v>7.1630000000000003</v>
       </c>
-      <c r="P34" s="9">
+      <c r="Q34" s="9">
         <v>0.92032800000000003</v>
       </c>
-      <c r="Q34" s="9">
+      <c r="R34" s="9">
         <v>0.89</v>
       </c>
-      <c r="R34" s="9">
+      <c r="S34" s="9">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="S34" s="9">
+      <c r="T34" s="9">
         <v>5.4</v>
       </c>
-      <c r="T34" s="9">
+      <c r="U34" s="9">
         <v>19.8</v>
       </c>
-      <c r="U34" s="9">
+      <c r="V34" s="9">
         <v>43.5</v>
       </c>
-      <c r="V34" s="9">
+      <c r="W34" s="9">
         <v>0.45525433300000001</v>
       </c>
-      <c r="W34" s="9">
+      <c r="X34" s="9">
         <v>7.8301999999999996</v>
       </c>
-      <c r="X34" s="9">
+      <c r="Y34" s="9">
         <v>3.8202247191011236</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B35" s="7">
         <v>44111</v>
@@ -3326,61 +3245,64 @@
       <c r="G35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I35" s="6">
         <v>0</v>
       </c>
-      <c r="I35" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R35" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="S35" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="T35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U35" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="V35" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="W35" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="X35" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24">
+      <c r="J35" s="10">
+        <v>1.28</v>
+      </c>
+      <c r="K35" s="9">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L35" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="M35" s="9">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="N35" s="10">
+        <v>10.39</v>
+      </c>
+      <c r="O35" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="P35" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="R35" s="9">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="S35" s="9">
+        <v>2.4E-2</v>
+      </c>
+      <c r="T35" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="U35" s="9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="V35" s="9">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="W35" s="9">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="X35" s="9">
+        <v>7.024</v>
+      </c>
+      <c r="Y35" s="9">
+        <v>3.9470000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B36" s="7">
         <v>44152</v>
@@ -3400,61 +3322,64 @@
       <c r="G36" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="6">
         <v>17.616512918559181</v>
       </c>
-      <c r="I36" s="10">
+      <c r="J36" s="10">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J36" s="9">
+      <c r="K36" s="9">
         <v>0.47</v>
       </c>
-      <c r="K36" s="9">
+      <c r="L36" s="9">
         <v>1.5383000000000001E-2</v>
       </c>
-      <c r="L36" s="9">
+      <c r="M36" s="9">
         <v>0.3344130434782609</v>
       </c>
-      <c r="M36" s="10">
+      <c r="N36" s="10">
         <v>3.2729787234042558</v>
       </c>
-      <c r="N36" s="9">
+      <c r="O36" s="9">
         <v>8.9710000000000001</v>
       </c>
-      <c r="O36" s="9">
+      <c r="P36" s="9">
         <v>9.3140000000000001</v>
       </c>
-      <c r="P36" s="9">
+      <c r="Q36" s="9">
         <v>0.96320899999999998</v>
       </c>
-      <c r="Q36" s="9">
+      <c r="R36" s="9">
         <v>5.78</v>
       </c>
-      <c r="R36" s="9">
+      <c r="S36" s="9">
         <v>0.11509999999999999</v>
       </c>
-      <c r="S36" s="9">
+      <c r="T36" s="9">
         <v>2</v>
       </c>
-      <c r="T36" s="9">
+      <c r="U36" s="9">
         <v>44.3</v>
       </c>
-      <c r="U36" s="9">
+      <c r="V36" s="9">
         <v>117.6</v>
       </c>
-      <c r="V36" s="9">
+      <c r="W36" s="9">
         <v>0.37682542499999999</v>
       </c>
-      <c r="W36" s="9">
+      <c r="X36" s="9">
         <v>27.4057</v>
       </c>
-      <c r="X36" s="9">
+      <c r="Y36" s="9">
         <v>2.0588235294117645</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B37" s="7">
         <v>44153</v>
@@ -3474,61 +3399,64 @@
       <c r="G37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I37" s="6">
         <v>20.520934422936421</v>
       </c>
-      <c r="I37" s="10">
+      <c r="J37" s="10">
         <v>1.76</v>
       </c>
-      <c r="J37" s="9">
+      <c r="K37" s="9">
         <v>0.23</v>
       </c>
-      <c r="K37" s="9">
+      <c r="L37" s="9">
         <v>1.1473000000000001E-2</v>
       </c>
-      <c r="L37" s="9">
+      <c r="M37" s="9">
         <v>0.65187499999999998</v>
       </c>
-      <c r="M37" s="10">
+      <c r="N37" s="10">
         <v>4.9882608695652175</v>
       </c>
-      <c r="N37" s="9">
+      <c r="O37" s="9">
         <v>6.5519999999999996</v>
       </c>
-      <c r="O37" s="9">
+      <c r="P37" s="9">
         <v>6.7299999999999995</v>
       </c>
-      <c r="P37" s="9">
+      <c r="Q37" s="9">
         <v>0.97356500000000001</v>
       </c>
-      <c r="Q37" s="9">
+      <c r="R37" s="9">
         <v>6.3</v>
       </c>
-      <c r="R37" s="9">
+      <c r="S37" s="9">
         <v>0.1855</v>
       </c>
-      <c r="S37" s="9">
+      <c r="T37" s="9">
         <v>2.9</v>
       </c>
-      <c r="T37" s="9">
+      <c r="U37" s="9">
         <v>71.400000000000006</v>
       </c>
-      <c r="U37" s="9">
+      <c r="V37" s="9">
         <v>212.4</v>
       </c>
-      <c r="V37" s="9">
+      <c r="W37" s="9">
         <v>0.33618150000000002</v>
       </c>
-      <c r="W37" s="9">
+      <c r="X37" s="9">
         <v>33.623799999999996</v>
       </c>
-      <c r="X37" s="9">
+      <c r="Y37" s="9">
         <v>2.3174603174603172</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B38" s="7">
         <v>44176</v>
@@ -3548,61 +3476,64 @@
       <c r="G38" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" s="6">
         <v>1.6778074422219769</v>
       </c>
-      <c r="I38" s="10">
+      <c r="J38" s="10">
         <v>1.76</v>
       </c>
-      <c r="J38" s="9">
+      <c r="K38" s="9">
         <v>0.09</v>
       </c>
-      <c r="K38" s="9">
+      <c r="L38" s="9">
         <v>5.8989999999999997E-3</v>
       </c>
-      <c r="L38" s="9">
+      <c r="M38" s="9">
         <v>0.33517045454545452</v>
       </c>
-      <c r="M38" s="10">
+      <c r="N38" s="10">
         <v>6.554444444444445</v>
       </c>
-      <c r="N38" s="9">
+      <c r="O38" s="9">
         <v>3.069</v>
       </c>
-      <c r="O38" s="9">
+      <c r="P38" s="9">
         <v>3.3639999999999999</v>
       </c>
-      <c r="P38" s="9">
+      <c r="Q38" s="9">
         <v>0.91233699999999995</v>
       </c>
-      <c r="Q38" s="9">
+      <c r="R38" s="9">
         <v>0.93</v>
       </c>
-      <c r="R38" s="9">
+      <c r="S38" s="9">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="S38" s="9">
+      <c r="T38" s="9">
         <v>3.5</v>
       </c>
-      <c r="T38" s="9">
+      <c r="U38" s="9">
         <v>13.299999999999999</v>
       </c>
-      <c r="U38" s="9">
+      <c r="V38" s="9">
         <v>28.6</v>
       </c>
-      <c r="V38" s="9">
+      <c r="W38" s="9">
         <v>0.46581750900000002</v>
       </c>
-      <c r="W38" s="9">
+      <c r="X38" s="9">
         <v>12.896799999999999</v>
       </c>
-      <c r="X38" s="9">
+      <c r="Y38" s="9">
         <v>6.021505376344086</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B39" s="7">
         <v>44178</v>
@@ -3622,61 +3553,64 @@
       <c r="G39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" s="6">
         <v>14.60129604344276</v>
       </c>
-      <c r="I39" s="10">
+      <c r="J39" s="10">
         <v>11.62</v>
       </c>
-      <c r="J39" s="9">
+      <c r="K39" s="9">
         <v>3.33</v>
       </c>
-      <c r="K39" s="9">
+      <c r="L39" s="9">
         <v>3.7698000000000002E-2</v>
       </c>
-      <c r="L39" s="9">
+      <c r="M39" s="9">
         <v>0.32442340791738389</v>
       </c>
-      <c r="M39" s="10">
+      <c r="N39" s="10">
         <v>1.1320720720720721</v>
       </c>
-      <c r="N39" s="9">
+      <c r="O39" s="9">
         <v>24.406000000000002</v>
       </c>
-      <c r="O39" s="9">
+      <c r="P39" s="9">
         <v>24.166</v>
       </c>
-      <c r="P39" s="9">
+      <c r="Q39" s="9">
         <v>1.0099389999999999</v>
       </c>
-      <c r="Q39" s="9">
+      <c r="R39" s="9">
         <v>6.36</v>
       </c>
-      <c r="R39" s="9">
+      <c r="S39" s="9">
         <v>0.19819999999999999</v>
       </c>
-      <c r="S39" s="9">
+      <c r="T39" s="9">
         <v>3.1</v>
       </c>
-      <c r="T39" s="9">
+      <c r="U39" s="9">
         <v>85.5</v>
       </c>
-      <c r="U39" s="9">
+      <c r="V39" s="9">
         <v>218</v>
       </c>
-      <c r="V39" s="9">
+      <c r="W39" s="9">
         <v>0.39225300699999999</v>
       </c>
-      <c r="W39" s="9">
+      <c r="X39" s="9">
         <v>43.756999999999998</v>
       </c>
-      <c r="X39" s="9">
+      <c r="Y39" s="9">
         <v>2.9874213836477987</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B40" s="7">
         <v>44200</v>
@@ -3696,61 +3630,64 @@
       <c r="G40" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="6">
         <v>3.7908334413193128</v>
       </c>
-      <c r="I40" s="10">
+      <c r="J40" s="10">
         <v>5.45</v>
       </c>
-      <c r="J40" s="9">
+      <c r="K40" s="9">
         <v>0.45</v>
       </c>
-      <c r="K40" s="9">
+      <c r="L40" s="9">
         <v>1.7454999999999998E-2</v>
       </c>
-      <c r="L40" s="9">
+      <c r="M40" s="9">
         <v>0.32027522935779812</v>
       </c>
-      <c r="M40" s="10">
+      <c r="N40" s="10">
         <v>3.8788888888888886</v>
       </c>
-      <c r="N40" s="9">
+      <c r="O40" s="9">
         <v>10.439</v>
       </c>
-      <c r="O40" s="9">
+      <c r="P40" s="9">
         <v>10.547000000000001</v>
       </c>
-      <c r="P40" s="9">
+      <c r="Q40" s="9">
         <v>0.98985000000000001</v>
       </c>
-      <c r="Q40" s="9">
+      <c r="R40" s="9">
         <v>4.6399999999999997</v>
       </c>
-      <c r="R40" s="9">
+      <c r="S40" s="9">
         <v>0.18379999999999999</v>
       </c>
-      <c r="S40" s="9">
+      <c r="T40" s="9">
         <v>4</v>
       </c>
-      <c r="T40" s="9">
+      <c r="U40" s="9">
         <v>82.4</v>
       </c>
-      <c r="U40" s="9">
+      <c r="V40" s="9">
         <v>194.5</v>
       </c>
-      <c r="V40" s="9">
+      <c r="W40" s="9">
         <v>0.42375015399999999</v>
       </c>
-      <c r="W40" s="9">
+      <c r="X40" s="9">
         <v>33.854099999999995</v>
       </c>
-      <c r="X40" s="9">
+      <c r="Y40" s="9">
         <v>3.1681034482758621</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B41" s="7">
         <v>44223</v>
@@ -3770,61 +3707,64 @@
       <c r="G41" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I41" s="6">
         <v>2.61165413845226</v>
       </c>
-      <c r="I41" s="10">
+      <c r="J41" s="10">
         <v>44.5</v>
       </c>
-      <c r="J41" s="9">
+      <c r="K41" s="9">
         <v>8.0299999999999994</v>
       </c>
-      <c r="K41" s="9">
+      <c r="L41" s="9">
         <v>0.155333</v>
       </c>
-      <c r="L41" s="9">
+      <c r="M41" s="9">
         <v>0.34906292134831457</v>
       </c>
-      <c r="M41" s="10">
+      <c r="N41" s="10">
         <v>1.9344084682440847</v>
       </c>
-      <c r="N41" s="9">
+      <c r="O41" s="9">
         <v>120.14700000000001</v>
       </c>
-      <c r="O41" s="9">
+      <c r="P41" s="9">
         <v>107.16800000000001</v>
       </c>
-      <c r="P41" s="9">
+      <c r="Q41" s="9">
         <v>1.1211040000000001</v>
       </c>
-      <c r="Q41" s="9">
+      <c r="R41" s="9">
         <v>5.39</v>
       </c>
-      <c r="R41" s="9">
+      <c r="S41" s="9">
         <v>0.28120000000000001</v>
       </c>
-      <c r="S41" s="9">
+      <c r="T41" s="9">
         <v>5.2</v>
       </c>
-      <c r="T41" s="9">
+      <c r="U41" s="9">
         <v>130.744</v>
       </c>
-      <c r="U41" s="9">
+      <c r="V41" s="9">
         <v>303.38499999999999</v>
       </c>
-      <c r="V41" s="9">
+      <c r="W41" s="9">
         <v>0.43095101499999999</v>
       </c>
-      <c r="W41" s="9">
+      <c r="X41" s="9">
         <v>38.920700000000004</v>
       </c>
-      <c r="X41" s="9">
+      <c r="Y41" s="9">
         <v>3.13543599257885</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B42" s="7">
         <v>44224</v>
@@ -3844,61 +3784,64 @@
       <c r="G42" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="6">
         <v>5.2549151260871296</v>
       </c>
-      <c r="I42" s="10">
+      <c r="J42" s="10">
         <v>533</v>
       </c>
-      <c r="J42" s="9">
+      <c r="K42" s="9">
         <v>12</v>
       </c>
-      <c r="K42" s="9">
+      <c r="L42" s="9">
         <v>0.348833</v>
       </c>
-      <c r="L42" s="9">
+      <c r="M42" s="9">
         <v>6.5447091932457777E-2</v>
       </c>
-      <c r="M42" s="10">
+      <c r="N42" s="10">
         <v>2.9069416666666665</v>
       </c>
-      <c r="N42" s="9">
+      <c r="O42" s="9">
         <v>275.93299999999999</v>
       </c>
-      <c r="O42" s="9">
+      <c r="P42" s="9">
         <v>273.06799999999998</v>
       </c>
-      <c r="P42" s="9">
+      <c r="Q42" s="9">
         <v>1.0104949999999999</v>
       </c>
-      <c r="Q42" s="9">
+      <c r="R42" s="9">
         <v>6.32</v>
       </c>
-      <c r="R42" s="9">
+      <c r="S42" s="9">
         <v>0.2024</v>
       </c>
-      <c r="S42" s="9">
+      <c r="T42" s="9">
         <v>3.2</v>
       </c>
-      <c r="T42" s="9">
+      <c r="U42" s="9">
         <v>89.6</v>
       </c>
-      <c r="U42" s="9">
+      <c r="V42" s="9">
         <v>213.7</v>
       </c>
-      <c r="V42" s="9">
+      <c r="W42" s="9">
         <v>0.41905857499999999</v>
       </c>
-      <c r="W42" s="9">
+      <c r="X42" s="9">
         <v>46.520600000000002</v>
       </c>
-      <c r="X42" s="9">
+      <c r="Y42" s="9">
         <v>3.1962025316455698</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B43" s="7">
         <v>44229</v>
@@ -3918,61 +3861,64 @@
       <c r="G43" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="6">
         <v>0.70439097072769874</v>
       </c>
-      <c r="I43" s="10">
+      <c r="J43" s="10">
         <v>18.920000000000002</v>
       </c>
-      <c r="J43" s="9">
+      <c r="K43" s="9">
         <v>0.87</v>
       </c>
-      <c r="K43" s="9">
+      <c r="L43" s="9">
         <v>5.3027999999999999E-2</v>
       </c>
-      <c r="L43" s="9">
+      <c r="M43" s="9">
         <v>0.28027484143763209</v>
       </c>
-      <c r="M43" s="10">
+      <c r="N43" s="10">
         <v>6.0951724137931036</v>
       </c>
-      <c r="N43" s="9">
+      <c r="O43" s="9">
         <v>36.081000000000003</v>
       </c>
-      <c r="O43" s="9">
+      <c r="P43" s="9">
         <v>34.371000000000002</v>
       </c>
-      <c r="P43" s="9">
+      <c r="Q43" s="9">
         <v>1.0497529999999999</v>
       </c>
-      <c r="Q43" s="9">
+      <c r="R43" s="9">
         <v>4.59</v>
       </c>
-      <c r="R43" s="9">
+      <c r="S43" s="9">
         <v>0.24379999999999999</v>
       </c>
-      <c r="S43" s="9">
+      <c r="T43" s="9">
         <v>5.3</v>
       </c>
-      <c r="T43" s="9">
+      <c r="U43" s="9">
         <v>120.70599999999999</v>
       </c>
-      <c r="U43" s="9">
+      <c r="V43" s="9">
         <v>250.77500000000003</v>
       </c>
-      <c r="V43" s="9">
+      <c r="W43" s="9">
         <v>0.48133368300000001</v>
       </c>
-      <c r="W43" s="9">
+      <c r="X43" s="9">
         <v>37.078299999999999</v>
       </c>
-      <c r="X43" s="9">
+      <c r="Y43" s="9">
         <v>3.507625272331155</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B44" s="7">
         <v>44273</v>
@@ -3992,61 +3938,64 @@
       <c r="G44" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="6">
         <v>1.1317445435788454</v>
       </c>
-      <c r="I44" s="10">
+      <c r="J44" s="10">
         <v>1.7</v>
       </c>
-      <c r="J44" s="9">
+      <c r="K44" s="9">
         <v>0.22</v>
       </c>
-      <c r="K44" s="9">
+      <c r="L44" s="9">
         <v>1.9611E-2</v>
       </c>
-      <c r="L44" s="9">
+      <c r="M44" s="9">
         <v>1.1535882352941178</v>
       </c>
-      <c r="M44" s="10">
+      <c r="N44" s="10">
         <v>8.9140909090909091</v>
       </c>
-      <c r="N44" s="9">
+      <c r="O44" s="9">
         <v>11.875999999999999</v>
       </c>
-      <c r="O44" s="9">
+      <c r="P44" s="9">
         <v>11.950000000000001</v>
       </c>
-      <c r="P44" s="9">
+      <c r="Q44" s="9">
         <v>0.993788</v>
       </c>
-      <c r="Q44" s="9">
+      <c r="R44" s="9">
         <v>3.49</v>
       </c>
-      <c r="R44" s="9">
+      <c r="S44" s="9">
         <v>0.14230000000000001</v>
       </c>
-      <c r="S44" s="9">
+      <c r="T44" s="9">
         <v>4.0999999999999996</v>
       </c>
-      <c r="T44" s="9">
+      <c r="U44" s="9">
         <v>65.3</v>
       </c>
-      <c r="U44" s="9">
+      <c r="V44" s="9">
         <v>142.5</v>
       </c>
-      <c r="V44" s="9">
+      <c r="W44" s="9">
         <v>0.45827815399999999</v>
       </c>
-      <c r="W44" s="9">
+      <c r="X44" s="9">
         <v>28.787499999999998</v>
       </c>
-      <c r="X44" s="9">
+      <c r="Y44" s="9">
         <v>3.5816618911174785</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B45" s="7">
         <v>44318</v>
@@ -4066,67 +4015,70 @@
       <c r="G45" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="6">
         <v>0.68856306062210049</v>
       </c>
-      <c r="I45" s="10">
+      <c r="J45" s="10">
         <v>0.27</v>
       </c>
-      <c r="J45" s="9">
+      <c r="K45" s="9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K45" s="9">
+      <c r="L45" s="9">
         <v>2.745E-3</v>
       </c>
-      <c r="L45" s="9">
+      <c r="M45" s="9">
         <v>1.0166666666666666</v>
       </c>
-      <c r="M45" s="10">
+      <c r="N45" s="10">
         <v>0.9803571428571427</v>
       </c>
-      <c r="N45" s="9">
+      <c r="O45" s="9">
         <v>1.3619999999999999</v>
       </c>
-      <c r="O45" s="9">
+      <c r="P45" s="9">
         <v>1.4319999999999999</v>
       </c>
-      <c r="P45" s="9">
+      <c r="Q45" s="9">
         <v>0.95112099999999999</v>
       </c>
-      <c r="Q45" s="9">
+      <c r="R45" s="9">
         <v>0.73</v>
       </c>
-      <c r="R45" s="9">
+      <c r="S45" s="9">
         <v>3.5099999999999999E-2</v>
       </c>
-      <c r="S45" s="9">
+      <c r="T45" s="9">
         <v>4.8</v>
       </c>
-      <c r="T45" s="9">
+      <c r="U45" s="9">
         <v>14.9</v>
       </c>
-      <c r="U45" s="9">
+      <c r="V45" s="9">
         <v>30</v>
       </c>
-      <c r="V45" s="9">
+      <c r="W45" s="9">
         <v>0.49711186099999999</v>
       </c>
-      <c r="W45" s="9">
+      <c r="X45" s="9">
         <v>7.8301999999999996</v>
       </c>
-      <c r="X45" s="9">
+      <c r="Y45" s="9">
         <v>4.6575342465753424</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B46" s="7">
         <v>44111</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D46" s="6">
         <v>37.054091999999997</v>
@@ -4140,61 +4092,64 @@
       <c r="G46" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="6">
         <v>1.7569469927499668</v>
       </c>
-      <c r="I46" s="10">
+      <c r="J46" s="10">
         <v>0.93</v>
       </c>
-      <c r="J46" s="9">
+      <c r="K46" s="9">
         <v>0.12</v>
       </c>
-      <c r="K46" s="9">
+      <c r="L46" s="9">
         <v>5.1019999999999998E-3</v>
       </c>
-      <c r="L46" s="9">
+      <c r="M46" s="9">
         <v>0.54860215053763439</v>
       </c>
-      <c r="M46" s="10">
+      <c r="N46" s="10">
         <v>4.2516666666666669</v>
       </c>
-      <c r="N46" s="9">
+      <c r="O46" s="9">
         <v>2.4550000000000001</v>
       </c>
-      <c r="O46" s="9">
+      <c r="P46" s="9">
         <v>3.0370000000000004</v>
       </c>
-      <c r="P46" s="9">
+      <c r="Q46" s="9">
         <v>0.808392</v>
       </c>
-      <c r="Q46" s="9">
+      <c r="R46" s="9">
         <v>1.64</v>
       </c>
-      <c r="R46" s="9">
+      <c r="S46" s="9">
         <v>7.46E-2</v>
       </c>
-      <c r="S46" s="9">
+      <c r="T46" s="9">
         <v>4.5999999999999996</v>
       </c>
-      <c r="T46" s="9">
+      <c r="U46" s="9">
         <v>28.032</v>
       </c>
-      <c r="U46" s="9">
+      <c r="V46" s="9">
         <v>74.668999999999997</v>
       </c>
-      <c r="V46" s="9">
+      <c r="W46" s="9">
         <v>0.37541585100000002</v>
       </c>
-      <c r="W46" s="9">
+      <c r="X46" s="9">
         <v>14.048299999999999</v>
       </c>
-      <c r="X46" s="9">
+      <c r="Y46" s="9">
         <v>3.719512195121951</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B47" s="7">
         <v>44153</v>
@@ -4214,61 +4169,64 @@
       <c r="G47" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="6">
         <v>33.33362765341802</v>
       </c>
-      <c r="I47" s="10">
+      <c r="J47" s="10">
         <v>3.35</v>
       </c>
-      <c r="J47" s="9">
+      <c r="K47" s="9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="K47" s="9">
+      <c r="L47" s="9">
         <v>6.8339999999999998E-3</v>
       </c>
-      <c r="L47" s="9">
+      <c r="M47" s="9">
         <v>0.20399999999999996</v>
       </c>
-      <c r="M47" s="10">
+      <c r="N47" s="10">
         <v>1.1989473684210528</v>
       </c>
-      <c r="N47" s="9">
+      <c r="O47" s="9">
         <v>3.4790000000000001</v>
       </c>
-      <c r="O47" s="9">
+      <c r="P47" s="9">
         <v>4.0720000000000001</v>
       </c>
-      <c r="P47" s="9">
+      <c r="Q47" s="9">
         <v>0.854294</v>
       </c>
-      <c r="Q47" s="9">
+      <c r="R47" s="9">
         <v>5.39</v>
       </c>
-      <c r="R47" s="9">
+      <c r="S47" s="9">
         <v>0.13189999999999999</v>
       </c>
-      <c r="S47" s="9">
+      <c r="T47" s="9">
         <v>2.4</v>
       </c>
-      <c r="T47" s="9">
+      <c r="U47" s="9">
         <v>51.3</v>
       </c>
-      <c r="U47" s="9">
+      <c r="V47" s="9">
         <v>139.80000000000001</v>
       </c>
-      <c r="V47" s="9">
+      <c r="W47" s="9">
         <v>0.366824492</v>
       </c>
-      <c r="W47" s="9">
+      <c r="X47" s="9">
         <v>27.866299999999999</v>
       </c>
-      <c r="X47" s="9">
+      <c r="Y47" s="9">
         <v>2.2448979591836737</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B48" s="7">
         <v>44176</v>
@@ -4288,61 +4246,64 @@
       <c r="G48" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I48" s="6">
         <v>1.851914453383555</v>
       </c>
-      <c r="I48" s="10">
+      <c r="J48" s="10">
         <v>0.35</v>
       </c>
-      <c r="J48" s="9">
+      <c r="K48" s="9">
         <v>0.13</v>
       </c>
-      <c r="K48" s="9">
+      <c r="L48" s="9">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="L48" s="9">
+      <c r="M48" s="9">
         <v>1.5428571428571431</v>
       </c>
-      <c r="M48" s="10">
+      <c r="N48" s="10">
         <v>4.1538461538461542</v>
       </c>
-      <c r="N48" s="9">
+      <c r="O48" s="9">
         <v>2.94</v>
       </c>
-      <c r="O48" s="9">
+      <c r="P48" s="9">
         <v>2.9020000000000001</v>
       </c>
-      <c r="P48" s="9">
+      <c r="Q48" s="9">
         <v>1.0132369999999999</v>
       </c>
-      <c r="Q48" s="9">
+      <c r="R48" s="9">
         <v>1.84</v>
       </c>
-      <c r="R48" s="9">
+      <c r="S48" s="9">
         <v>9.1499999999999998E-2</v>
       </c>
-      <c r="S48" s="9">
+      <c r="T48" s="9">
         <v>4.9710943089999997</v>
       </c>
-      <c r="T48" s="9">
+      <c r="U48" s="9">
         <v>35</v>
       </c>
-      <c r="U48" s="9">
+      <c r="V48" s="9">
         <v>92.600000000000009</v>
       </c>
-      <c r="V48" s="9">
+      <c r="W48" s="9">
         <v>0.37802443600000002</v>
       </c>
-      <c r="W48" s="9">
+      <c r="X48" s="9">
         <v>11.284700000000001</v>
       </c>
-      <c r="X48" s="9">
+      <c r="Y48" s="9">
         <v>2.6630434782608696</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B49" s="7">
         <v>44178</v>
@@ -4362,61 +4323,64 @@
       <c r="G49" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="6">
         <v>4.3685521601736408</v>
       </c>
-      <c r="I49" s="10">
+      <c r="J49" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J49" s="9">
+      <c r="K49" s="9">
         <v>0.5</v>
       </c>
-      <c r="K49" s="9">
+      <c r="L49" s="9">
         <v>3.9280000000000001E-3</v>
       </c>
-      <c r="L49" s="9">
+      <c r="M49" s="9">
         <v>0.35709090909090907</v>
       </c>
-      <c r="M49" s="10">
+      <c r="N49" s="10">
         <v>0.78559999999999997</v>
       </c>
-      <c r="N49" s="9">
+      <c r="O49" s="9">
         <v>1.887</v>
       </c>
-      <c r="O49" s="9">
+      <c r="P49" s="9">
         <v>2.242</v>
       </c>
-      <c r="P49" s="9">
+      <c r="Q49" s="9">
         <v>0.841611</v>
       </c>
-      <c r="Q49" s="9">
+      <c r="R49" s="9">
         <v>3.7</v>
       </c>
-      <c r="R49" s="9">
+      <c r="S49" s="9">
         <v>0.14099999999999999</v>
       </c>
-      <c r="S49" s="9">
+      <c r="T49" s="9">
         <v>3.8</v>
       </c>
-      <c r="T49" s="9">
+      <c r="U49" s="9">
         <v>58.7</v>
       </c>
-      <c r="U49" s="9">
+      <c r="V49" s="9">
         <v>148.4</v>
       </c>
-      <c r="V49" s="9">
+      <c r="W49" s="9">
         <v>0.39553918300000002</v>
       </c>
-      <c r="W49" s="9">
+      <c r="X49" s="9">
         <v>23.951199999999996</v>
       </c>
-      <c r="X49" s="9">
+      <c r="Y49" s="9">
         <v>2.8108108108108105</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B50" s="7">
         <v>44200</v>
@@ -4436,61 +4400,64 @@
       <c r="G50" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" s="6">
         <v>1.741119082644369</v>
       </c>
-      <c r="I50" s="10">
+      <c r="J50" s="10">
         <v>0.45</v>
       </c>
-      <c r="J50" s="9">
+      <c r="K50" s="9">
         <v>0.46</v>
       </c>
-      <c r="K50" s="9">
+      <c r="L50" s="9">
         <v>3.2469999999999999E-3</v>
       </c>
-      <c r="L50" s="9">
+      <c r="M50" s="9">
         <v>0.72155555555555551</v>
       </c>
-      <c r="M50" s="10">
+      <c r="N50" s="10">
         <v>0.70586956521739119</v>
       </c>
-      <c r="N50" s="9">
+      <c r="O50" s="9">
         <v>1.4450000000000001</v>
       </c>
-      <c r="O50" s="9">
+      <c r="P50" s="9">
         <v>1.911</v>
       </c>
-      <c r="P50" s="9">
+      <c r="Q50" s="9">
         <v>0.75611799999999996</v>
       </c>
-      <c r="Q50" s="9">
+      <c r="R50" s="9">
         <v>3.01</v>
       </c>
-      <c r="R50" s="9">
+      <c r="S50" s="9">
         <v>0.11849999999999999</v>
       </c>
-      <c r="S50" s="9">
+      <c r="T50" s="9">
         <v>3.9</v>
       </c>
-      <c r="T50" s="9">
+      <c r="U50" s="9">
         <v>50.1</v>
       </c>
-      <c r="U50" s="9">
+      <c r="V50" s="9">
         <v>122.6</v>
       </c>
-      <c r="V50" s="9">
+      <c r="W50" s="9">
         <v>0.40909784199999999</v>
       </c>
-      <c r="W50" s="9">
+      <c r="X50" s="9">
         <v>18.423999999999999</v>
       </c>
-      <c r="X50" s="9">
+      <c r="Y50" s="9">
         <v>2.6578073089701002</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="11" customFormat="1">
+    <row r="51" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B51" s="12">
         <v>44223</v>
@@ -4510,61 +4477,64 @@
       <c r="G51" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51" s="11">
         <v>0.72813283588609545</v>
       </c>
-      <c r="I51" s="15">
+      <c r="J51" s="15">
         <v>1031</v>
       </c>
-      <c r="J51" s="14">
+      <c r="K51" s="14">
         <v>27.75</v>
       </c>
-      <c r="K51" s="14">
+      <c r="L51" s="14">
         <v>1.4931129999999999</v>
       </c>
-      <c r="L51" s="14">
+      <c r="M51" s="14">
         <v>0.14482182347235692</v>
       </c>
-      <c r="M51" s="15">
+      <c r="N51" s="15">
         <v>5.3805873873873873</v>
       </c>
-      <c r="N51" s="14">
+      <c r="O51" s="14">
         <v>1341.424</v>
       </c>
-      <c r="O51" s="14">
+      <c r="P51" s="14">
         <v>1336.693</v>
       </c>
-      <c r="P51" s="14">
+      <c r="Q51" s="14">
         <v>1.003539</v>
       </c>
-      <c r="Q51" s="14">
+      <c r="R51" s="14">
         <v>10.88</v>
       </c>
-      <c r="R51" s="14">
+      <c r="S51" s="14">
         <v>0.42320000000000002</v>
       </c>
-      <c r="S51" s="14">
+      <c r="T51" s="14">
         <v>3.9</v>
       </c>
-      <c r="T51" s="14">
+      <c r="U51" s="14">
         <v>173.815</v>
       </c>
-      <c r="U51" s="14">
+      <c r="V51" s="14">
         <v>503.88799999999998</v>
       </c>
-      <c r="V51" s="14">
+      <c r="W51" s="14">
         <v>0.34494709800000001</v>
       </c>
-      <c r="W51" s="14">
+      <c r="X51" s="14">
         <v>65.405199999999994</v>
       </c>
-      <c r="X51" s="14">
+      <c r="Y51" s="14">
         <v>2.6102941176470584</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="11" customFormat="1">
+    <row r="52" spans="1:25" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B52" s="12">
         <v>44224</v>
@@ -4584,61 +4554,64 @@
       <c r="G52" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52" s="11">
         <v>1.9310540039115454</v>
       </c>
-      <c r="I52" s="15">
+      <c r="J52" s="15">
         <v>1603</v>
       </c>
-      <c r="J52" s="14">
+      <c r="K52" s="14">
         <v>39.270000000000003</v>
       </c>
-      <c r="K52" s="14">
+      <c r="L52" s="14">
         <v>1.4774099999999999</v>
       </c>
-      <c r="L52" s="14">
+      <c r="M52" s="14">
         <v>9.2165315034310663E-2</v>
       </c>
-      <c r="M52" s="15">
+      <c r="N52" s="15">
         <v>3.7621848739495789</v>
       </c>
-      <c r="N52" s="14">
+      <c r="O52" s="14">
         <v>1211.518</v>
       </c>
-      <c r="O52" s="14">
+      <c r="P52" s="14">
         <v>1435.9170000000001</v>
       </c>
-      <c r="P52" s="14">
+      <c r="Q52" s="14">
         <v>0.84372400000000003</v>
       </c>
-      <c r="Q52" s="14">
+      <c r="R52" s="14">
         <v>9.82</v>
       </c>
-      <c r="R52" s="14">
+      <c r="S52" s="14">
         <v>0.442</v>
       </c>
-      <c r="S52" s="14">
+      <c r="T52" s="14">
         <v>4.5</v>
       </c>
-      <c r="T52" s="14">
+      <c r="U52" s="14">
         <v>187.15300000000002</v>
       </c>
-      <c r="U52" s="14">
+      <c r="V52" s="14">
         <v>523.44000000000005</v>
       </c>
-      <c r="V52" s="14">
+      <c r="W52" s="14">
         <v>0.35754395700000002</v>
       </c>
-      <c r="W52" s="14">
+      <c r="X52" s="14">
         <v>54.581099999999992</v>
       </c>
-      <c r="X52" s="14">
+      <c r="Y52" s="14">
         <v>2.4134419551934827</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B53" s="7">
         <v>44229</v>
@@ -4658,61 +4631,64 @@
       <c r="G53" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" s="6">
         <v>8.4838087876291262</v>
       </c>
-      <c r="I53" s="10">
+      <c r="J53" s="10">
         <v>740.5</v>
       </c>
-      <c r="J53" s="9">
+      <c r="K53" s="9">
         <v>30.44</v>
       </c>
-      <c r="K53" s="9">
+      <c r="L53" s="9">
         <v>0.81612499999999999</v>
       </c>
-      <c r="L53" s="9">
+      <c r="M53" s="9">
         <v>0.11021269412559082</v>
       </c>
-      <c r="M53" s="10">
+      <c r="N53" s="10">
         <v>2.6810939553219448</v>
       </c>
-      <c r="N53" s="9">
+      <c r="O53" s="9">
         <v>624.80599999999993</v>
       </c>
-      <c r="O53" s="9">
+      <c r="P53" s="9">
         <v>761.64600000000007</v>
       </c>
-      <c r="P53" s="9">
+      <c r="Q53" s="9">
         <v>0.82033699999999998</v>
       </c>
-      <c r="Q53" s="9">
+      <c r="R53" s="9">
         <v>6.45</v>
       </c>
-      <c r="R53" s="9">
+      <c r="S53" s="9">
         <v>0.31530000000000002</v>
       </c>
-      <c r="S53" s="9">
+      <c r="T53" s="9">
         <v>4.9000000000000004</v>
       </c>
-      <c r="T53" s="9">
+      <c r="U53" s="9">
         <v>135.36100000000002</v>
       </c>
-      <c r="U53" s="9">
+      <c r="V53" s="9">
         <v>356.45600000000002</v>
       </c>
-      <c r="V53" s="9">
+      <c r="W53" s="9">
         <v>0.37974231400000003</v>
       </c>
-      <c r="W53" s="9">
+      <c r="X53" s="9">
         <v>38.690400000000004</v>
       </c>
-      <c r="X53" s="9">
+      <c r="Y53" s="9">
         <v>2.6046511627906979</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B54" s="7">
         <v>44273</v>
@@ -4732,61 +4708,64 @@
       <c r="G54" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" s="6">
         <v>1.3533352850572173</v>
       </c>
-      <c r="I54" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="L54" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="N54" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="P54" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q54" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="R54" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="S54" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="T54" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="U54" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="V54" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="W54" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="X54" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24">
+      <c r="J54" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="K54" s="9">
+        <v>6.84</v>
+      </c>
+      <c r="L54" s="9">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="M54" s="9">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="N54" s="10">
+        <v>6.86</v>
+      </c>
+      <c r="O54" s="9">
+        <v>225.4</v>
+      </c>
+      <c r="P54" s="9">
+        <v>243.2</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="R54" s="9">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="S54" s="9">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="T54" s="9">
+        <v>7.6509999999999998</v>
+      </c>
+      <c r="U54" s="9">
+        <v>58.7</v>
+      </c>
+      <c r="V54" s="9">
+        <v>152.4</v>
+      </c>
+      <c r="W54" s="9">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="X54" s="9">
+        <v>17.388000000000002</v>
+      </c>
+      <c r="Y54" s="9">
+        <v>3.8809999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B55" s="7">
         <v>44318</v>
@@ -4806,55 +4785,58 @@
       <c r="G55" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I55" s="6">
         <v>2.1289028802315206</v>
       </c>
-      <c r="I55" s="10">
+      <c r="J55" s="10">
         <v>4.62</v>
       </c>
-      <c r="J55" s="9">
+      <c r="K55" s="9">
         <v>0.43</v>
       </c>
-      <c r="K55" s="9">
+      <c r="L55" s="9">
         <v>3.2691999999999999E-2</v>
       </c>
-      <c r="L55" s="9">
+      <c r="M55" s="9">
         <v>0.70761904761904759</v>
       </c>
-      <c r="M55" s="10">
+      <c r="N55" s="10">
         <v>7.6027906976744175</v>
       </c>
-      <c r="N55" s="9">
+      <c r="O55" s="9">
         <v>20.032999999999998</v>
       </c>
-      <c r="O55" s="9">
+      <c r="P55" s="9">
         <v>21.552000000000003</v>
       </c>
-      <c r="P55" s="9">
+      <c r="Q55" s="9">
         <v>0.92952199999999996</v>
       </c>
-      <c r="Q55" s="9">
+      <c r="R55" s="9">
         <v>1.81</v>
       </c>
-      <c r="R55" s="9">
+      <c r="S55" s="9">
         <v>0.10539999999999999</v>
       </c>
-      <c r="S55" s="9">
+      <c r="T55" s="9">
         <v>5.8246090949999996</v>
       </c>
-      <c r="T55" s="9">
+      <c r="U55" s="9">
         <v>41.5</v>
       </c>
-      <c r="U55" s="9">
+      <c r="V55" s="9">
         <v>107.5</v>
       </c>
-      <c r="V55" s="9">
+      <c r="W55" s="9">
         <v>0.38567544500000001</v>
       </c>
-      <c r="W55" s="9">
+      <c r="X55" s="9">
         <v>14.739199999999999</v>
       </c>
-      <c r="X55" s="9">
+      <c r="Y55" s="9">
         <v>3.535911602209945</v>
       </c>
     </row>
